--- a/Excel/家具表.xlsx
+++ b/Excel/家具表.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -45,8 +45,16 @@
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +64,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF6E243E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004F81BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,10 +89,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -440,18 +464,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:T42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27.875" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="10"/>
     <col width="14.375" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="73.625" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="15"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="15"/>
     <col width="12" customWidth="1" min="16" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -463,82 +487,97 @@
           <t>id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>英文索引</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>表面类型</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>占格列</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>占格行</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>显示宽</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>显示高</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>装饰分</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>精灵图</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>拿起音效</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>放下音效</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>桌面格启用</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>桌面格列数</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>桌面格宽</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>桌面格高</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>桌面格偏移X</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>桌面高度</t>
         </is>
@@ -550,82 +589,97 @@
           <t>id</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>nameKey</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>surface</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>cols</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>rows</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>displayWidth</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>displayHeight</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>decorationScore</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>sprite</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>pickupSound</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>putdownSound</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>tableSurface.enabled</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>tableSurface.cols</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>tableSurface.cellWidth</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>tableSurface.cellHeight</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>tableSurface.offsetX</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>tableSurface.surfaceHeight</t>
         </is>
@@ -644,52 +698,67 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>红色扶手椅</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
       <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>185</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>174</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>32</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/002_red_armchair 1.png</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>64</v>
-      </c>
-      <c r="O3" t="n">
-        <v>56</v>
-      </c>
       <c r="P3" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
+        <v>64</v>
+      </c>
+      <c r="R3" t="n">
+        <v>56</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="n">
         <v>146</v>
       </c>
     </row>
@@ -706,52 +775,67 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>落地灯</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>灯具</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>77</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>194</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>15</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/003_floor_lamp 4.png</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>64</v>
-      </c>
-      <c r="O4" t="n">
-        <v>56</v>
-      </c>
       <c r="P4" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="n">
+        <v>64</v>
+      </c>
+      <c r="R4" t="n">
+        <v>56</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="n">
         <v>146</v>
       </c>
     </row>
@@ -768,52 +852,67 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>装饰书柜</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
         <v>153</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>255</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>39</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/004_decorated_bookcase 1.png</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>64</v>
-      </c>
-      <c r="O5" t="n">
-        <v>56</v>
-      </c>
       <c r="P5" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
+        <v>64</v>
+      </c>
+      <c r="R5" t="n">
+        <v>56</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="n">
         <v>146</v>
       </c>
     </row>
@@ -830,52 +929,67 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>木质茶几</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>4</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>252</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>110</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>28</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/005_wood_coffee_table 1.png</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="N6" t="n">
-        <v>64</v>
-      </c>
-      <c r="O6" t="n">
-        <v>56</v>
-      </c>
-      <c r="P6" t="n">
-        <v>50</v>
-      </c>
       <c r="Q6" t="n">
+        <v>64</v>
+      </c>
+      <c r="R6" t="n">
+        <v>56</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="n">
         <v>88</v>
       </c>
     </row>
@@ -892,52 +1006,67 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>蓝色圆柱桌</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>94</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>113</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>11</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/006_blue_pedestal_table 3.png</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="n">
-        <v>64</v>
-      </c>
-      <c r="O7" t="n">
-        <v>56</v>
-      </c>
-      <c r="P7" t="n">
-        <v>50</v>
-      </c>
       <c r="Q7" t="n">
+        <v>64</v>
+      </c>
+      <c r="R7" t="n">
+        <v>56</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="n">
         <v>90</v>
       </c>
     </row>
@@ -954,52 +1083,67 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>悬挂绿植·壹</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
       <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
         <v>86</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>188</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>16</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/007_hanging_plant_1 4.png</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>64</v>
-      </c>
-      <c r="O8" t="n">
-        <v>56</v>
-      </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="n">
+        <v>64</v>
+      </c>
+      <c r="R8" t="n">
+        <v>56</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1016,52 +1160,67 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>悬挂绿植·贰</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>76</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>137</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>10</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/008_hanging_plant_2 3.png</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" t="n">
-        <v>64</v>
-      </c>
-      <c r="O9" t="n">
-        <v>56</v>
-      </c>
       <c r="P9" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
+        <v>64</v>
+      </c>
+      <c r="R9" t="n">
+        <v>56</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1078,52 +1237,67 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>悬挂绿植·肆</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>壁挂</t>
         </is>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
         <v>90</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>124</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>11</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/010_hanging_plant_4 2.png</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N10" t="n">
-        <v>64</v>
-      </c>
-      <c r="O10" t="n">
-        <v>56</v>
-      </c>
       <c r="P10" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
+        <v>64</v>
+      </c>
+      <c r="R10" t="n">
+        <v>56</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1140,52 +1314,67 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>敞口纸箱</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>摆件</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>地面/桌面</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>131</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>84</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>11</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/011_open_cardboard_box 1.png</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>3</v>
-      </c>
-      <c r="N11" t="n">
-        <v>64</v>
-      </c>
-      <c r="O11" t="n">
-        <v>56</v>
-      </c>
       <c r="P11" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
+        <v>64</v>
+      </c>
+      <c r="R11" t="n">
+        <v>56</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1202,52 +1391,67 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>封口纸箱</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>摆件</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>地面/桌面</t>
         </is>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
         <v>91</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>76</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>7</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/012_closed_cardboard_box 1.png</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>3</v>
-      </c>
-      <c r="N12" t="n">
-        <v>64</v>
-      </c>
-      <c r="O12" t="n">
-        <v>56</v>
-      </c>
       <c r="P12" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
+        <v>64</v>
+      </c>
+      <c r="R12" t="n">
+        <v>56</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1264,52 +1468,67 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>龟背竹盆栽·壹</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>盆栽</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F13" t="n">
-        <v>2</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
         <v>124</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>160</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>20</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/013_potted_monstera_1 5.png</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>3</v>
-      </c>
-      <c r="N13" t="n">
-        <v>64</v>
-      </c>
-      <c r="O13" t="n">
-        <v>56</v>
-      </c>
       <c r="P13" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
+        <v>64</v>
+      </c>
+      <c r="R13" t="n">
+        <v>56</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1326,52 +1545,67 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>龟背竹盆栽·贰</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>盆栽</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
         <v>102</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>119</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>12</v>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/014_potted_monstera_2 4.png</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>64</v>
-      </c>
-      <c r="O14" t="n">
-        <v>56</v>
-      </c>
       <c r="P14" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
+        <v>64</v>
+      </c>
+      <c r="R14" t="n">
+        <v>56</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1388,52 +1622,67 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>山景海报</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>壁挂</t>
         </is>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="n">
         <v>94</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>115</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>11</v>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/016_mountain_poster 3.png</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>3</v>
-      </c>
-      <c r="N15" t="n">
-        <v>64</v>
-      </c>
-      <c r="O15" t="n">
-        <v>56</v>
-      </c>
       <c r="P15" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
+        <v>64</v>
+      </c>
+      <c r="R15" t="n">
+        <v>56</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1450,52 +1699,67 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>挂钟</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>壁挂</t>
         </is>
-      </c>
-      <c r="F16" t="n">
-        <v>1</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
         <v>75</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>81</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>6</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/017_wall_clock 2.png</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>3</v>
-      </c>
-      <c r="N16" t="n">
-        <v>64</v>
-      </c>
-      <c r="O16" t="n">
-        <v>56</v>
-      </c>
       <c r="P16" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
+        <v>64</v>
+      </c>
+      <c r="R16" t="n">
+        <v>56</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1512,52 +1776,67 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>挂历</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>壁挂</t>
         </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
+        <v>64</v>
+      </c>
+      <c r="J17" t="n">
         <v>72</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>5</v>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/018_wall_calendar 2.png</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>64</v>
-      </c>
-      <c r="O17" t="n">
-        <v>56</v>
-      </c>
       <c r="P17" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
+        <v>64</v>
+      </c>
+      <c r="R17" t="n">
+        <v>56</v>
+      </c>
+      <c r="S17" t="n">
+        <v>50</v>
+      </c>
+      <c r="T17" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1574,52 +1853,67 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>绿色挂签</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>壁挂</t>
         </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>52</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>38</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/020_green_tag 1.png</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N18" t="n">
-        <v>64</v>
-      </c>
-      <c r="O18" t="n">
-        <v>56</v>
-      </c>
       <c r="P18" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
+        <v>64</v>
+      </c>
+      <c r="R18" t="n">
+        <v>56</v>
+      </c>
+      <c r="S18" t="n">
+        <v>50</v>
+      </c>
+      <c r="T18" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1636,52 +1930,67 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>紫色挂签</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>壁挂</t>
         </is>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
         <v>51</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>38</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>5</v>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/021_purple_tag 1.png</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N19" t="n">
-        <v>64</v>
-      </c>
-      <c r="O19" t="n">
-        <v>56</v>
-      </c>
       <c r="P19" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
+        <v>64</v>
+      </c>
+      <c r="R19" t="n">
+        <v>56</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1698,52 +2007,67 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>悬挂绿植</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>2</v>
       </c>
-      <c r="G20" t="n">
-        <v>3</v>
-      </c>
       <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
         <v>95</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>209</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>20</v>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/023_hanging_plant 3.png</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>64</v>
-      </c>
-      <c r="O20" t="n">
-        <v>56</v>
-      </c>
       <c r="P20" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
+        <v>64</v>
+      </c>
+      <c r="R20" t="n">
+        <v>56</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1760,52 +2084,67 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>蓝色沙发</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>5</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>316</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>138</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>44</v>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/024_blue_sofa 2.png</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>64</v>
-      </c>
-      <c r="O21" t="n">
-        <v>56</v>
-      </c>
       <c r="P21" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
+        <v>64</v>
+      </c>
+      <c r="R21" t="n">
+        <v>56</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1822,52 +2161,67 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>敞口纸箱·大</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>摆件</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>地面/桌面</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>1</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>111</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>95</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>11</v>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/032_open_cardboard_box 1.png</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N22" t="n">
-        <v>64</v>
-      </c>
-      <c r="O22" t="n">
-        <v>56</v>
-      </c>
       <c r="P22" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
+        <v>64</v>
+      </c>
+      <c r="R22" t="n">
+        <v>56</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1884,52 +2238,67 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>书立文件架</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>摆件</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
       </c>
       <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
         <v>92</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>72</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>7</v>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/035_book_file_holder 2.png</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M23" t="n">
-        <v>3</v>
-      </c>
-      <c r="N23" t="n">
-        <v>64</v>
-      </c>
-      <c r="O23" t="n">
-        <v>56</v>
-      </c>
       <c r="P23" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
+        <v>64</v>
+      </c>
+      <c r="R23" t="n">
+        <v>56</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="n">
         <v>146</v>
       </c>
     </row>
@@ -1946,52 +2315,67 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>圆形太空椅</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F24" t="n">
-        <v>2</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
         <v>173</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>195</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>34</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/036_round_pod_chair 1.png</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M24" t="n">
-        <v>3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>64</v>
-      </c>
-      <c r="O24" t="n">
-        <v>56</v>
-      </c>
       <c r="P24" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
+        <v>64</v>
+      </c>
+      <c r="R24" t="n">
+        <v>56</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2008,52 +2392,67 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>云形壁镜</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>壁挂</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>壁挂</t>
         </is>
-      </c>
-      <c r="F25" t="n">
-        <v>2</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
       </c>
       <c r="H25" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
         <v>96</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>131</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>13</v>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/037_organic_wall_mirror 2.png</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>64</v>
-      </c>
-      <c r="O25" t="n">
-        <v>56</v>
-      </c>
       <c r="P25" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
+        <v>64</v>
+      </c>
+      <c r="R25" t="n">
+        <v>56</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2070,52 +2469,67 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>圆球落地灯</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>灯具</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>1</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>85</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>165</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>14</v>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/038_orb_floor_lamp 4.png</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>3</v>
-      </c>
-      <c r="N26" t="n">
-        <v>64</v>
-      </c>
-      <c r="O26" t="n">
-        <v>56</v>
-      </c>
       <c r="P26" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
+        <v>64</v>
+      </c>
+      <c r="R26" t="n">
+        <v>56</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2132,52 +2546,67 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>水母缸边柜</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
       </c>
       <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
         <v>158</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>187</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>30</v>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/040_jellyfish_aquarium_console 2.png</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" t="n">
-        <v>64</v>
-      </c>
-      <c r="O27" t="n">
-        <v>56</v>
-      </c>
       <c r="P27" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
+        <v>64</v>
+      </c>
+      <c r="R27" t="n">
+        <v>56</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2194,52 +2623,67 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>熔岩灯</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>灯具</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>2</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>60</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>183</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>11</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/041_lava_lamp 3.png</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M28" t="n">
-        <v>3</v>
-      </c>
-      <c r="N28" t="n">
-        <v>64</v>
-      </c>
-      <c r="O28" t="n">
-        <v>56</v>
-      </c>
       <c r="P28" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
+        <v>64</v>
+      </c>
+      <c r="R28" t="n">
+        <v>56</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2256,52 +2700,67 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>复古餐桌椅</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>5</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>2</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>369</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>184</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>60</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/043_retro_dining_set 4.png</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="M29" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>64</v>
-      </c>
-      <c r="O29" t="n">
-        <v>56</v>
-      </c>
       <c r="P29" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
+        <v>64</v>
+      </c>
+      <c r="R29" t="n">
+        <v>56</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="n">
         <v>147</v>
       </c>
     </row>
@@ -2318,52 +2777,67 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>仙人掌灯</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>灯具</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
         <v>70</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>121</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>8</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/049_cactus_lamp 3.png</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>3</v>
-      </c>
-      <c r="N30" t="n">
-        <v>64</v>
-      </c>
-      <c r="O30" t="n">
-        <v>56</v>
-      </c>
       <c r="P30" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
+        <v>64</v>
+      </c>
+      <c r="R30" t="n">
+        <v>56</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2380,52 +2854,67 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>圆形吧台架</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F31" t="n">
-        <v>2</v>
       </c>
       <c r="G31" t="n">
         <v>2</v>
       </c>
       <c r="H31" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" t="n">
         <v>124</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>163</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>20</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/051_round_bar_shelf 2.png</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M31" t="n">
-        <v>3</v>
-      </c>
-      <c r="N31" t="n">
-        <v>64</v>
-      </c>
-      <c r="O31" t="n">
-        <v>56</v>
-      </c>
       <c r="P31" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
+        <v>64</v>
+      </c>
+      <c r="R31" t="n">
+        <v>56</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2442,52 +2931,67 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>棕榈盆栽</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>盆栽</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>2</v>
       </c>
-      <c r="G32" t="n">
-        <v>3</v>
-      </c>
       <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
         <v>130</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>301</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>39</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/053_potted_palm 3.png</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M32" t="n">
-        <v>3</v>
-      </c>
-      <c r="N32" t="n">
-        <v>64</v>
-      </c>
-      <c r="O32" t="n">
-        <v>56</v>
-      </c>
       <c r="P32" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
+        <v>64</v>
+      </c>
+      <c r="R32" t="n">
+        <v>56</v>
+      </c>
+      <c r="S32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2504,52 +3008,67 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>蓝色懒人沙发</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>1</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>140</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>112</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>16</v>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/054_blue_beanbag 1.png</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M33" t="n">
-        <v>3</v>
-      </c>
-      <c r="N33" t="n">
-        <v>64</v>
-      </c>
-      <c r="O33" t="n">
-        <v>56</v>
-      </c>
       <c r="P33" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
+        <v>64</v>
+      </c>
+      <c r="R33" t="n">
+        <v>56</v>
+      </c>
+      <c r="S33" t="n">
+        <v>50</v>
+      </c>
+      <c r="T33" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2566,52 +3085,67 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
+          <t>太空地毯</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t>摆件</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>3</v>
-      </c>
       <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
         <v>1</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>194</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>79</v>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>15</v>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/055_space_rug 2.png</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M34" t="n">
-        <v>3</v>
-      </c>
-      <c r="N34" t="n">
-        <v>64</v>
-      </c>
-      <c r="O34" t="n">
-        <v>56</v>
-      </c>
       <c r="P34" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
+        <v>64</v>
+      </c>
+      <c r="R34" t="n">
+        <v>56</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2628,52 +3162,67 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>云朵茶几</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>4</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>1</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>275</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>119</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>33</v>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/056_cloud_coffee_table 1.png</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="M35" t="n">
-        <v>3</v>
-      </c>
-      <c r="N35" t="n">
-        <v>64</v>
-      </c>
-      <c r="O35" t="n">
-        <v>56</v>
-      </c>
       <c r="P35" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
+        <v>64</v>
+      </c>
+      <c r="R35" t="n">
+        <v>56</v>
+      </c>
+      <c r="S35" t="n">
+        <v>50</v>
+      </c>
+      <c r="T35" t="n">
         <v>95</v>
       </c>
     </row>
@@ -2690,52 +3239,67 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>玻璃电视柜</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>4</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>1</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>303</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>136</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>41</v>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/057_glass_media_console 2.png</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M36" t="n">
-        <v>3</v>
-      </c>
-      <c r="N36" t="n">
-        <v>64</v>
-      </c>
-      <c r="O36" t="n">
-        <v>56</v>
-      </c>
       <c r="P36" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
+        <v>64</v>
+      </c>
+      <c r="R36" t="n">
+        <v>56</v>
+      </c>
+      <c r="S36" t="n">
+        <v>50</v>
+      </c>
+      <c r="T36" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2752,52 +3316,67 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>月牙水族灯</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>灯具</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F37" t="n">
-        <v>2</v>
       </c>
       <c r="G37" t="n">
         <v>2</v>
       </c>
       <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="n">
         <v>114</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>160</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>18</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/059_crescent_aquarium_lamp 3.png</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M37" t="n">
-        <v>3</v>
-      </c>
-      <c r="N37" t="n">
-        <v>64</v>
-      </c>
-      <c r="O37" t="n">
-        <v>56</v>
-      </c>
       <c r="P37" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
+        <v>64</v>
+      </c>
+      <c r="R37" t="n">
+        <v>56</v>
+      </c>
+      <c r="S37" t="n">
+        <v>50</v>
+      </c>
+      <c r="T37" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2814,52 +3393,67 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
+          <t>复古太空电视</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
           <t>摆件</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F38" t="n">
-        <v>2</v>
       </c>
       <c r="G38" t="n">
         <v>2</v>
       </c>
       <c r="H38" t="n">
+        <v>2</v>
+      </c>
+      <c r="I38" t="n">
         <v>148</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>140</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>21</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/060_retro_space_tv 2.png</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M38" t="n">
-        <v>3</v>
-      </c>
-      <c r="N38" t="n">
-        <v>64</v>
-      </c>
-      <c r="O38" t="n">
-        <v>56</v>
-      </c>
       <c r="P38" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
+        <v>64</v>
+      </c>
+      <c r="R38" t="n">
+        <v>56</v>
+      </c>
+      <c r="S38" t="n">
+        <v>50</v>
+      </c>
+      <c r="T38" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2876,52 +3470,67 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
+          <t>熔岩灯·高</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>灯具</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>1</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>2</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>65</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>181</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>12</v>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/063_lava_lamp 1.png</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M39" t="n">
-        <v>3</v>
-      </c>
-      <c r="N39" t="n">
-        <v>64</v>
-      </c>
-      <c r="O39" t="n">
-        <v>56</v>
-      </c>
       <c r="P39" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
+        <v>64</v>
+      </c>
+      <c r="R39" t="n">
+        <v>56</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50</v>
+      </c>
+      <c r="T39" t="n">
         <v>146</v>
       </c>
     </row>
@@ -2938,52 +3547,67 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>高筒气泡水族箱</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>摆件</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>2</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>62</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>208</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>13</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/064_tall_bubble_aquarium 1.png</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M40" t="n">
-        <v>3</v>
-      </c>
-      <c r="N40" t="n">
-        <v>64</v>
-      </c>
-      <c r="O40" t="n">
-        <v>56</v>
-      </c>
       <c r="P40" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
+        <v>64</v>
+      </c>
+      <c r="R40" t="n">
+        <v>56</v>
+      </c>
+      <c r="S40" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" t="n">
         <v>146</v>
       </c>
     </row>
@@ -3000,52 +3624,67 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
+          <t>洗衣机</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
           <t>摆件</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
-      </c>
-      <c r="F41" t="n">
-        <v>2</v>
       </c>
       <c r="G41" t="n">
         <v>2</v>
       </c>
       <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
         <v>161</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>188</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>30</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/075_washing_machine 1.png</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M41" t="n">
-        <v>3</v>
-      </c>
-      <c r="N41" t="n">
-        <v>64</v>
-      </c>
-      <c r="O41" t="n">
-        <v>56</v>
-      </c>
       <c r="P41" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
+        <v>64</v>
+      </c>
+      <c r="R41" t="n">
+        <v>56</v>
+      </c>
+      <c r="S41" t="n">
+        <v>50</v>
+      </c>
+      <c r="T41" t="n">
         <v>146</v>
       </c>
     </row>
@@ -3062,52 +3701,67 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>浴缸茶座</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>桌椅</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>地面</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="G42" t="n">
         <v>5</v>
       </c>
-      <c r="G42" t="n">
-        <v>3</v>
-      </c>
       <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
         <v>363</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>294</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>60</v>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Assets/PC ui/Scene/furniture/077_bathtub_table_set 1.png</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Pickup_260813_1</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>SoundEffect/2_Putdown_260813</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="M42" t="n">
-        <v>3</v>
-      </c>
-      <c r="N42" t="n">
-        <v>64</v>
-      </c>
-      <c r="O42" t="n">
-        <v>56</v>
-      </c>
       <c r="P42" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
+        <v>64</v>
+      </c>
+      <c r="R42" t="n">
+        <v>56</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="n">
         <v>146</v>
       </c>
     </row>

--- a/Excel/家具表.xlsx
+++ b/Excel/家具表.xlsx
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>39</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>39</v>
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>39</v>
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>39</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>39</v>
@@ -1174,10 +1174,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>39</v>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>200</v>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>200</v>
@@ -1435,10 +1435,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>200</v>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
         <v>200</v>
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>200</v>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
         <v>200</v>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
         <v>200</v>
@@ -1870,10 +1870,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
         <v>200</v>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
         <v>65</v>
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>64</v>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>62</v>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>72</v>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
         <v>150</v>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
         <v>150</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
         <v>150</v>
@@ -2566,10 +2566,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>150</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>150</v>
@@ -2740,10 +2740,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>150</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>150</v>
@@ -2914,10 +2914,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>150</v>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>185</v>
@@ -3088,10 +3088,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>185</v>
@@ -3175,10 +3175,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>185</v>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>185</v>
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>185</v>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>185</v>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>185</v>
@@ -3610,10 +3610,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>185</v>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>185</v>
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>185</v>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
         <v>185</v>
@@ -3958,10 +3958,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>185</v>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>56</v>
@@ -4132,10 +4132,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
         <v>63</v>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" t="n">
         <v>58</v>
@@ -4306,10 +4306,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
         <v>44</v>
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
         <v>45</v>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J46" t="n">
         <v>97</v>
@@ -4567,10 +4567,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J47" t="n">
         <v>90</v>
@@ -4654,10 +4654,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J48" t="n">
         <v>93</v>
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
         <v>95</v>
@@ -4828,10 +4828,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
         <v>93</v>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>83</v>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
         <v>101</v>
@@ -5089,10 +5089,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
         <v>55</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
         <v>76</v>
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J55" t="n">
         <v>92</v>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J56" t="n">
         <v>74</v>
@@ -5437,10 +5437,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I57" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J57" t="n">
         <v>80</v>
@@ -5524,10 +5524,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I58" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J58" t="n">
         <v>90</v>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I59" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J59" t="n">
         <v>72</v>
@@ -5698,10 +5698,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I60" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J60" t="n">
         <v>64</v>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J61" t="n">
         <v>66</v>
@@ -5872,10 +5872,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J62" t="n">
         <v>86</v>
@@ -5959,10 +5959,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I63" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J63" t="n">
         <v>65</v>
@@ -6046,10 +6046,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I64" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J64" t="n">
         <v>83</v>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I65" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J65" t="n">
         <v>84</v>
@@ -6220,10 +6220,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J66" t="n">
         <v>102</v>
@@ -6307,10 +6307,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I67" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J67" t="n">
         <v>86</v>
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
         <v>81</v>
@@ -6481,10 +6481,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I69" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J69" t="n">
         <v>79</v>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J70" t="n">
         <v>79</v>
@@ -6655,10 +6655,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J71" t="n">
         <v>79</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J72" t="n">
         <v>79</v>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
         <v>80</v>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J74" t="n">
         <v>81</v>
@@ -7003,10 +7003,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J75" t="n">
         <v>80</v>
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
         <v>30</v>
@@ -7177,10 +7177,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J77" t="n">
         <v>31</v>
@@ -7264,10 +7264,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>30</v>
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J79" t="n">
         <v>31</v>
@@ -7438,10 +7438,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>31</v>
@@ -7525,10 +7525,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
         <v>30</v>
@@ -7612,10 +7612,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
         <v>38</v>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J83" t="n">
         <v>30</v>
@@ -7786,10 +7786,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I84" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J84" t="n">
         <v>126</v>
@@ -7873,10 +7873,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J85" t="n">
         <v>122</v>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J86" t="n">
         <v>132</v>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J87" t="n">
         <v>116</v>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J88" t="n">
         <v>131</v>
@@ -8221,10 +8221,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J89" t="n">
         <v>128</v>
@@ -8308,10 +8308,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J90" t="n">
         <v>120</v>
@@ -8395,10 +8395,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" t="n">
         <v>41</v>
@@ -8482,10 +8482,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
         <v>42</v>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J93" t="n">
         <v>50</v>
@@ -8656,10 +8656,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J94" t="n">
         <v>43</v>
@@ -8743,10 +8743,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>41</v>
@@ -8830,10 +8830,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
         <v>38</v>
@@ -8917,10 +8917,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J97" t="n">
         <v>42</v>
@@ -9004,10 +9004,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
         <v>41</v>
@@ -9091,10 +9091,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J99" t="n">
         <v>41</v>
@@ -9178,10 +9178,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J100" t="n">
         <v>52</v>
@@ -9265,10 +9265,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
         <v>51</v>
@@ -9352,10 +9352,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
         <v>51</v>
@@ -9439,10 +9439,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>47</v>
@@ -9526,10 +9526,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
         <v>48</v>
@@ -9613,10 +9613,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
         <v>200</v>
@@ -9700,10 +9700,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J106" t="n">
         <v>200</v>
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J107" t="n">
         <v>200</v>
@@ -9874,10 +9874,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
         <v>200</v>
@@ -9961,10 +9961,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J109" t="n">
         <v>200</v>
@@ -10048,10 +10048,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
         <v>200</v>
@@ -10135,10 +10135,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
         <v>200</v>
@@ -10222,10 +10222,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
         <v>200</v>
@@ -10309,10 +10309,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J113" t="n">
         <v>200</v>
@@ -10396,10 +10396,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I114" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J114" t="n">
         <v>200</v>
@@ -10483,10 +10483,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>86</v>
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
         <v>87</v>
@@ -10657,10 +10657,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
         <v>86</v>
@@ -10744,10 +10744,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J118" t="n">
         <v>84</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="n">
         <v>85</v>
@@ -10918,10 +10918,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
         <v>86</v>
@@ -11005,10 +11005,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
         <v>84</v>
@@ -11092,10 +11092,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J122" t="n">
         <v>85</v>
@@ -11179,10 +11179,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J123" t="n">
         <v>83</v>

--- a/Excel/家具表.xlsx
+++ b/Excel/家具表.xlsx
@@ -1264,7 +1264,7 @@
         <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>200</v>
@@ -1351,7 +1351,7 @@
         <v>6</v>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>200</v>
@@ -1438,7 +1438,7 @@
         <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>200</v>
@@ -1525,7 +1525,7 @@
         <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>200</v>
@@ -1612,7 +1612,7 @@
         <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>200</v>
@@ -1699,7 +1699,7 @@
         <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>200</v>
@@ -1786,7 +1786,7 @@
         <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>200</v>
@@ -1873,7 +1873,7 @@
         <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>200</v>
@@ -2308,7 +2308,7 @@
         <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>150</v>
@@ -2395,7 +2395,7 @@
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>150</v>
@@ -2482,7 +2482,7 @@
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>150</v>
@@ -2569,7 +2569,7 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>150</v>
@@ -2656,7 +2656,7 @@
         <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>150</v>
@@ -2743,7 +2743,7 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>150</v>
@@ -2830,7 +2830,7 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>150</v>
@@ -2917,7 +2917,7 @@
         <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>150</v>
@@ -3004,7 +3004,7 @@
         <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>185</v>
@@ -3091,7 +3091,7 @@
         <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>185</v>
@@ -3178,7 +3178,7 @@
         <v>6</v>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>185</v>
@@ -3265,7 +3265,7 @@
         <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>185</v>
@@ -3352,7 +3352,7 @@
         <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>185</v>
@@ -3439,7 +3439,7 @@
         <v>6</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>185</v>
@@ -3526,7 +3526,7 @@
         <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J35" t="n">
         <v>185</v>
@@ -3613,7 +3613,7 @@
         <v>6</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>185</v>
@@ -3700,7 +3700,7 @@
         <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J37" t="n">
         <v>185</v>
@@ -3787,7 +3787,7 @@
         <v>6</v>
       </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>185</v>
@@ -3874,7 +3874,7 @@
         <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>185</v>
@@ -3961,7 +3961,7 @@
         <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>185</v>
@@ -7789,7 +7789,7 @@
         <v>4</v>
       </c>
       <c r="I84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J84" t="n">
         <v>126</v>
@@ -7876,7 +7876,7 @@
         <v>4</v>
       </c>
       <c r="I85" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J85" t="n">
         <v>122</v>
@@ -7963,7 +7963,7 @@
         <v>4</v>
       </c>
       <c r="I86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
         <v>132</v>
@@ -8050,7 +8050,7 @@
         <v>4</v>
       </c>
       <c r="I87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J87" t="n">
         <v>116</v>
@@ -8137,7 +8137,7 @@
         <v>4</v>
       </c>
       <c r="I88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
         <v>131</v>
@@ -8224,7 +8224,7 @@
         <v>4</v>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J89" t="n">
         <v>128</v>
@@ -8311,7 +8311,7 @@
         <v>4</v>
       </c>
       <c r="I90" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J90" t="n">
         <v>120</v>

--- a/Excel/家具表.xlsx
+++ b/Excel/家具表.xlsx
@@ -2344,12 +2344,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>71</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2428,12 +2428,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>40</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>54</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>53</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>47</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>61</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>75</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>117</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">

--- a/Excel/家具表.xlsx
+++ b/Excel/家具表.xlsx
@@ -5582,7 +5582,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>178</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>196</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>136</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>182</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">

--- a/Excel/家具表.xlsx
+++ b/Excel/家具表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具" sheetId="1" r:id="R9e7f9e7ae43a4422"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具" sheetId="1" r:id="R41c6267c0f8a4dff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -344,6 +344,8 @@
     <x:col min="6" max="6" width="9" customWidth="1"/>
     <x:col min="7" max="7" width="52" customWidth="1"/>
     <x:col min="8" max="8" width="10" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -387,6 +389,12 @@
           <x:t xml:space="preserve">色值</x:t>
         </x:is>
       </x:c>
+      <x:c r="I1" t="str">
+        <x:v>商店显示宽</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>商店显示高</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="1" t="inlineStr">
@@ -429,6 +437,12 @@
           <x:t xml:space="preserve">swatchColor</x:t>
         </x:is>
       </x:c>
+      <x:c r="I2" t="str">
+        <x:v>storeDisplayWidth</x:v>
+      </x:c>
+      <x:c r="J2" t="str">
+        <x:v>storeDisplayHeight</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="inlineStr">
@@ -441,10 +455,8 @@
           <x:t xml:space="preserve">table_lamp_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">台灯·01</x:t>
-        </x:is>
+      <x:c r="C3" t="str">
+        <x:v>经典落地灯·01</x:v>
       </x:c>
       <x:c r="D3" t="inlineStr">
         <x:is>
@@ -452,10 +464,10 @@
         </x:is>
       </x:c>
       <x:c r="E3" s="2" t="n">
-        <x:v>26</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F3" s="2" t="n">
-        <x:v>75</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G3" t="inlineStr">
         <x:is>
@@ -466,6 +478,12 @@
         <x:is>
           <x:t xml:space="preserve">#D5B061</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I3" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J3" t="n">
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -479,10 +497,8 @@
           <x:t xml:space="preserve">table_lamp_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">台灯·02</x:t>
-        </x:is>
+      <x:c r="C4" t="str">
+        <x:v>经典落地灯·02</x:v>
       </x:c>
       <x:c r="D4" t="inlineStr">
         <x:is>
@@ -490,10 +506,10 @@
         </x:is>
       </x:c>
       <x:c r="E4" s="2" t="n">
-        <x:v>26</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F4" s="2" t="n">
-        <x:v>75</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G4" t="inlineStr">
         <x:is>
@@ -504,6 +520,12 @@
         <x:is>
           <x:t xml:space="preserve">#C0AF97</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I4" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J4" t="n">
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -517,10 +539,8 @@
           <x:t xml:space="preserve">table_lamp_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">台灯·03</x:t>
-        </x:is>
+      <x:c r="C5" t="str">
+        <x:v>经典落地灯·03</x:v>
       </x:c>
       <x:c r="D5" t="inlineStr">
         <x:is>
@@ -528,10 +548,10 @@
         </x:is>
       </x:c>
       <x:c r="E5" s="2" t="n">
-        <x:v>26</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F5" s="2" t="n">
-        <x:v>75</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G5" t="inlineStr">
         <x:is>
@@ -542,6 +562,12 @@
         <x:is>
           <x:t xml:space="preserve">#CCA49C</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I5" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J5" t="n">
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -555,10 +581,8 @@
           <x:t xml:space="preserve">table_lamp_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">台灯·04</x:t>
-        </x:is>
+      <x:c r="C6" t="str">
+        <x:v>经典落地灯·04</x:v>
       </x:c>
       <x:c r="D6" t="inlineStr">
         <x:is>
@@ -566,10 +590,10 @@
         </x:is>
       </x:c>
       <x:c r="E6" s="2" t="n">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F6" s="2" t="n">
-        <x:v>75</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G6" t="inlineStr">
         <x:is>
@@ -580,6 +604,12 @@
         <x:is>
           <x:t xml:space="preserve">#9C9F83</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I6" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J6" t="n">
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -593,10 +623,8 @@
           <x:t xml:space="preserve">table_lamp_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">台灯·05</x:t>
-        </x:is>
+      <x:c r="C7" t="str">
+        <x:v>经典落地灯·05</x:v>
       </x:c>
       <x:c r="D7" t="inlineStr">
         <x:is>
@@ -604,10 +632,10 @@
         </x:is>
       </x:c>
       <x:c r="E7" s="2" t="n">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F7" s="2" t="n">
-        <x:v>75</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G7" t="inlineStr">
         <x:is>
@@ -618,6 +646,12 @@
         <x:is>
           <x:t xml:space="preserve">#A3AFBD</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I7" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J7" t="n">
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -631,10 +665,8 @@
           <x:t xml:space="preserve">table_lamp_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">台灯·06</x:t>
-        </x:is>
+      <x:c r="C8" t="str">
+        <x:v>经典落地灯·06</x:v>
       </x:c>
       <x:c r="D8" t="inlineStr">
         <x:is>
@@ -642,10 +674,10 @@
         </x:is>
       </x:c>
       <x:c r="E8" s="2" t="n">
-        <x:v>26</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F8" s="2" t="n">
-        <x:v>75</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G8" t="inlineStr">
         <x:is>
@@ -656,6 +688,12 @@
         <x:is>
           <x:t xml:space="preserve">#AB95A0</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J8" t="n">
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -669,10 +707,8 @@
           <x:t xml:space="preserve">round_table_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆桌·01</x:t>
-        </x:is>
+      <x:c r="C9" t="str">
+        <x:v>圆桌·01</x:v>
       </x:c>
       <x:c r="D9" t="inlineStr">
         <x:is>
@@ -680,10 +716,10 @@
         </x:is>
       </x:c>
       <x:c r="E9" s="2" t="n">
-        <x:v>120</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F9" s="2" t="n">
-        <x:v>162</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G9" t="inlineStr">
         <x:is>
@@ -694,6 +730,12 @@
         <x:is>
           <x:t xml:space="preserve">#8EABC2</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J9" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -707,10 +749,8 @@
           <x:t xml:space="preserve">round_table_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆桌·02</x:t>
-        </x:is>
+      <x:c r="C10" t="str">
+        <x:v>圆桌·02</x:v>
       </x:c>
       <x:c r="D10" t="inlineStr">
         <x:is>
@@ -718,10 +758,10 @@
         </x:is>
       </x:c>
       <x:c r="E10" s="2" t="n">
-        <x:v>120</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F10" s="2" t="n">
-        <x:v>154</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G10" t="inlineStr">
         <x:is>
@@ -732,6 +772,12 @@
         <x:is>
           <x:t xml:space="preserve">#ACB189</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I10" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J10" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -745,10 +791,8 @@
           <x:t xml:space="preserve">round_table_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆桌·03</x:t>
-        </x:is>
+      <x:c r="C11" t="str">
+        <x:v>圆桌·03</x:v>
       </x:c>
       <x:c r="D11" t="inlineStr">
         <x:is>
@@ -756,20 +800,26 @@
         </x:is>
       </x:c>
       <x:c r="E11" s="2" t="n">
-        <x:v>120</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F11" s="2" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Assets/PC ui/Scene/furniture/03_圆桌 1.png</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">#E07A60</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J11" t="n">
         <x:v>155</x:v>
-      </x:c>
-      <x:c r="G11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Assets/PC ui/Scene/furniture/03_圆桌 1.png</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">#E07A60</x:t>
-        </x:is>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -783,10 +833,8 @@
           <x:t xml:space="preserve">round_table_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆桌·04</x:t>
-        </x:is>
+      <x:c r="C12" t="str">
+        <x:v>圆桌·04</x:v>
       </x:c>
       <x:c r="D12" t="inlineStr">
         <x:is>
@@ -794,10 +842,10 @@
         </x:is>
       </x:c>
       <x:c r="E12" s="2" t="n">
-        <x:v>120</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F12" s="2" t="n">
-        <x:v>158</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G12" t="inlineStr">
         <x:is>
@@ -808,6 +856,12 @@
         <x:is>
           <x:t xml:space="preserve">#E5D1B2</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I12" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J12" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -821,10 +875,8 @@
           <x:t xml:space="preserve">round_table_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆桌·05</x:t>
-        </x:is>
+      <x:c r="C13" t="str">
+        <x:v>圆桌·05</x:v>
       </x:c>
       <x:c r="D13" t="inlineStr">
         <x:is>
@@ -832,10 +884,10 @@
         </x:is>
       </x:c>
       <x:c r="E13" s="2" t="n">
-        <x:v>120</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F13" s="2" t="n">
-        <x:v>160</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G13" t="inlineStr">
         <x:is>
@@ -846,6 +898,12 @@
         <x:is>
           <x:t xml:space="preserve">#697075</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I13" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J13" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -859,10 +917,8 @@
           <x:t xml:space="preserve">round_table_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆桌·06</x:t>
-        </x:is>
+      <x:c r="C14" t="str">
+        <x:v>圆桌·06</x:v>
       </x:c>
       <x:c r="D14" t="inlineStr">
         <x:is>
@@ -870,10 +926,10 @@
         </x:is>
       </x:c>
       <x:c r="E14" s="2" t="n">
-        <x:v>120</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F14" s="2" t="n">
-        <x:v>157</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G14" t="inlineStr">
         <x:is>
@@ -884,6 +940,12 @@
         <x:is>
           <x:t xml:space="preserve">#E7C374</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I14" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J14" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -897,10 +959,8 @@
           <x:t xml:space="preserve">round_table_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆桌·07</x:t>
-        </x:is>
+      <x:c r="C15" t="str">
+        <x:v>圆桌·07</x:v>
       </x:c>
       <x:c r="D15" t="inlineStr">
         <x:is>
@@ -908,10 +968,10 @@
         </x:is>
       </x:c>
       <x:c r="E15" s="2" t="n">
-        <x:v>120</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F15" s="2" t="n">
-        <x:v>160</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G15" t="inlineStr">
         <x:is>
@@ -922,6 +982,12 @@
         <x:is>
           <x:t xml:space="preserve">#E9BAB1</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I15" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J15" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -935,10 +1001,8 @@
           <x:t xml:space="preserve">round_table_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆桌·08</x:t>
-        </x:is>
+      <x:c r="C16" t="str">
+        <x:v>圆桌·08</x:v>
       </x:c>
       <x:c r="D16" t="inlineStr">
         <x:is>
@@ -946,10 +1010,10 @@
         </x:is>
       </x:c>
       <x:c r="E16" s="2" t="n">
-        <x:v>120</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F16" s="2" t="n">
-        <x:v>161</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G16" t="inlineStr">
         <x:is>
@@ -960,6 +1024,12 @@
         <x:is>
           <x:t xml:space="preserve">#B1C7B9</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I16" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J16" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -973,10 +1043,8 @@
           <x:t xml:space="preserve">crescent_aquarium_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月牙鱼缸·01</x:t>
-        </x:is>
+      <x:c r="C17" t="str">
+        <x:v>月牙鱼缸·01</x:v>
       </x:c>
       <x:c r="D17" t="inlineStr">
         <x:is>
@@ -984,10 +1052,10 @@
         </x:is>
       </x:c>
       <x:c r="E17" s="2" t="n">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F17" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G17" t="inlineStr">
         <x:is>
@@ -998,6 +1066,12 @@
         <x:is>
           <x:t xml:space="preserve">#B1C5C6</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I17" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J17" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1011,10 +1085,8 @@
           <x:t xml:space="preserve">crescent_aquarium_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月牙鱼缸·04</x:t>
-        </x:is>
+      <x:c r="C18" t="str">
+        <x:v>月牙鱼缸·04</x:v>
       </x:c>
       <x:c r="D18" t="inlineStr">
         <x:is>
@@ -1022,10 +1094,10 @@
         </x:is>
       </x:c>
       <x:c r="E18" s="2" t="n">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F18" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G18" t="inlineStr">
         <x:is>
@@ -1036,6 +1108,12 @@
         <x:is>
           <x:t xml:space="preserve">#B4A8B8</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I18" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J18" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1049,10 +1127,8 @@
           <x:t xml:space="preserve">crescent_aquarium_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月牙鱼缸·05</x:t>
-        </x:is>
+      <x:c r="C19" t="str">
+        <x:v>月牙鱼缸·05</x:v>
       </x:c>
       <x:c r="D19" t="inlineStr">
         <x:is>
@@ -1060,10 +1136,10 @@
         </x:is>
       </x:c>
       <x:c r="E19" s="2" t="n">
-        <x:v>38</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F19" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G19" t="inlineStr">
         <x:is>
@@ -1074,6 +1150,12 @@
         <x:is>
           <x:t xml:space="preserve">#D0D3B3</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I19" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J19" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1087,10 +1169,8 @@
           <x:t xml:space="preserve">crescent_aquarium_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">月牙鱼缸·07</x:t>
-        </x:is>
+      <x:c r="C20" t="str">
+        <x:v>月牙鱼缸·07</x:v>
       </x:c>
       <x:c r="D20" t="inlineStr">
         <x:is>
@@ -1098,10 +1178,10 @@
         </x:is>
       </x:c>
       <x:c r="E20" s="2" t="n">
-        <x:v>39</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F20" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G20" t="inlineStr">
         <x:is>
@@ -1112,6 +1192,12 @@
         <x:is>
           <x:t xml:space="preserve">#E4D6CA</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I20" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J20" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1125,10 +1211,8 @@
           <x:t xml:space="preserve">cat_sofa_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">猫耳懒人沙发·01</x:t>
-        </x:is>
+      <x:c r="C21" t="str">
+        <x:v>猫耳懒人沙发·01</x:v>
       </x:c>
       <x:c r="D21" t="inlineStr">
         <x:is>
@@ -1136,10 +1220,10 @@
         </x:is>
       </x:c>
       <x:c r="E21" s="2" t="n">
-        <x:v>110</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F21" s="2" t="n">
-        <x:v>94</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G21" t="inlineStr">
         <x:is>
@@ -1150,6 +1234,12 @@
         <x:is>
           <x:t xml:space="preserve">#96B2CB</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I21" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J21" t="n">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1163,10 +1253,8 @@
           <x:t xml:space="preserve">cat_sofa_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">猫耳懒人沙发·02</x:t>
-        </x:is>
+      <x:c r="C22" t="str">
+        <x:v>猫耳懒人沙发·02</x:v>
       </x:c>
       <x:c r="D22" t="inlineStr">
         <x:is>
@@ -1174,10 +1262,10 @@
         </x:is>
       </x:c>
       <x:c r="E22" s="2" t="n">
-        <x:v>110</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F22" s="2" t="n">
-        <x:v>97</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G22" t="inlineStr">
         <x:is>
@@ -1188,6 +1276,12 @@
         <x:is>
           <x:t xml:space="preserve">#E89276</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I22" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J22" t="n">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1201,10 +1295,8 @@
           <x:t xml:space="preserve">cat_sofa_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">猫耳懒人沙发·03</x:t>
-        </x:is>
+      <x:c r="C23" t="str">
+        <x:v>猫耳懒人沙发·03</x:v>
       </x:c>
       <x:c r="D23" t="inlineStr">
         <x:is>
@@ -1212,10 +1304,10 @@
         </x:is>
       </x:c>
       <x:c r="E23" s="2" t="n">
-        <x:v>110</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F23" s="2" t="n">
-        <x:v>98</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G23" t="inlineStr">
         <x:is>
@@ -1226,6 +1318,12 @@
         <x:is>
           <x:t xml:space="preserve">#A8BEA2</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I23" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J23" t="n">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1239,10 +1337,8 @@
           <x:t xml:space="preserve">cat_sofa_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">猫耳懒人沙发·04</x:t>
-        </x:is>
+      <x:c r="C24" t="str">
+        <x:v>猫耳懒人沙发·04</x:v>
       </x:c>
       <x:c r="D24" t="inlineStr">
         <x:is>
@@ -1250,10 +1346,10 @@
         </x:is>
       </x:c>
       <x:c r="E24" s="2" t="n">
-        <x:v>110</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F24" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G24" t="inlineStr">
         <x:is>
@@ -1264,6 +1360,12 @@
         <x:is>
           <x:t xml:space="preserve">#EDBD6F</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I24" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J24" t="n">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1277,10 +1379,8 @@
           <x:t xml:space="preserve">cat_sofa_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">猫耳懒人沙发·05</x:t>
-        </x:is>
+      <x:c r="C25" t="str">
+        <x:v>猫耳懒人沙发·05</x:v>
       </x:c>
       <x:c r="D25" t="inlineStr">
         <x:is>
@@ -1288,10 +1388,10 @@
         </x:is>
       </x:c>
       <x:c r="E25" s="2" t="n">
-        <x:v>110</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F25" s="2" t="n">
-        <x:v>97</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G25" t="inlineStr">
         <x:is>
@@ -1302,6 +1402,12 @@
         <x:is>
           <x:t xml:space="preserve">#C8B1BF</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I25" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J25" t="n">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1315,10 +1421,8 @@
           <x:t xml:space="preserve">cat_sofa_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">猫耳懒人沙发·06</x:t>
-        </x:is>
+      <x:c r="C26" t="str">
+        <x:v>猫耳懒人沙发·06</x:v>
       </x:c>
       <x:c r="D26" t="inlineStr">
         <x:is>
@@ -1326,10 +1430,10 @@
         </x:is>
       </x:c>
       <x:c r="E26" s="2" t="n">
-        <x:v>110</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F26" s="2" t="n">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G26" t="inlineStr">
         <x:is>
@@ -1340,6 +1444,12 @@
         <x:is>
           <x:t xml:space="preserve">#B5D4D9</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I26" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J26" t="n">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1353,10 +1463,8 @@
           <x:t xml:space="preserve">cat_sofa_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">猫耳懒人沙发·07</x:t>
-        </x:is>
+      <x:c r="C27" t="str">
+        <x:v>猫耳懒人沙发·07</x:v>
       </x:c>
       <x:c r="D27" t="inlineStr">
         <x:is>
@@ -1364,10 +1472,10 @@
         </x:is>
       </x:c>
       <x:c r="E27" s="2" t="n">
-        <x:v>110</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F27" s="2" t="n">
-        <x:v>93</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G27" t="inlineStr">
         <x:is>
@@ -1378,6 +1486,12 @@
         <x:is>
           <x:t xml:space="preserve">#8FA7BA</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J27" t="n">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1391,10 +1505,8 @@
           <x:t xml:space="preserve">cat_sofa_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C28" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">猫耳懒人沙发·08</x:t>
-        </x:is>
+      <x:c r="C28" t="str">
+        <x:v>猫耳懒人沙发·08</x:v>
       </x:c>
       <x:c r="D28" t="inlineStr">
         <x:is>
@@ -1402,10 +1514,10 @@
         </x:is>
       </x:c>
       <x:c r="E28" s="2" t="n">
-        <x:v>110</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F28" s="2" t="n">
-        <x:v>96</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G28" t="inlineStr">
         <x:is>
@@ -1416,6 +1528,12 @@
         <x:is>
           <x:t xml:space="preserve">#ECD2AA</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I28" t="n">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="J28" t="n">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1429,10 +1547,8 @@
           <x:t xml:space="preserve">single_sofa_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C29" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·02</x:t>
-        </x:is>
+      <x:c r="C29" t="str">
+        <x:v>单人沙发·02</x:v>
       </x:c>
       <x:c r="D29" t="inlineStr">
         <x:is>
@@ -1440,10 +1556,10 @@
         </x:is>
       </x:c>
       <x:c r="E29" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F29" s="2" t="n">
-        <x:v>114</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G29" t="inlineStr">
         <x:is>
@@ -1454,6 +1570,12 @@
         <x:is>
           <x:t xml:space="preserve">#3B4F63</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J29" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1467,10 +1589,8 @@
           <x:t xml:space="preserve">single_sofa_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C30" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·03</x:t>
-        </x:is>
+      <x:c r="C30" t="str">
+        <x:v>单人沙发·03</x:v>
       </x:c>
       <x:c r="D30" t="inlineStr">
         <x:is>
@@ -1478,10 +1598,10 @@
         </x:is>
       </x:c>
       <x:c r="E30" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F30" s="2" t="n">
-        <x:v>112</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G30" t="inlineStr">
         <x:is>
@@ -1492,6 +1612,12 @@
         <x:is>
           <x:t xml:space="preserve">#4E5B37</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I30" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J30" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1505,10 +1631,8 @@
           <x:t xml:space="preserve">single_sofa_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·04</x:t>
-        </x:is>
+      <x:c r="C31" t="str">
+        <x:v>单人沙发·04</x:v>
       </x:c>
       <x:c r="D31" t="inlineStr">
         <x:is>
@@ -1516,10 +1640,10 @@
         </x:is>
       </x:c>
       <x:c r="E31" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F31" s="2" t="n">
-        <x:v>113</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G31" t="inlineStr">
         <x:is>
@@ -1530,6 +1654,12 @@
         <x:is>
           <x:t xml:space="preserve">#A87219</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I31" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J31" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1543,10 +1673,8 @@
           <x:t xml:space="preserve">single_sofa_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C32" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·05</x:t>
-        </x:is>
+      <x:c r="C32" t="str">
+        <x:v>单人沙发·05</x:v>
       </x:c>
       <x:c r="D32" t="inlineStr">
         <x:is>
@@ -1554,10 +1682,10 @@
         </x:is>
       </x:c>
       <x:c r="E32" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F32" s="2" t="n">
-        <x:v>113</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G32" t="inlineStr">
         <x:is>
@@ -1568,6 +1696,12 @@
         <x:is>
           <x:t xml:space="preserve">#664E71</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I32" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J32" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -1581,10 +1715,8 @@
           <x:t xml:space="preserve">single_sofa_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C33" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·06</x:t>
-        </x:is>
+      <x:c r="C33" t="str">
+        <x:v>单人沙发·06</x:v>
       </x:c>
       <x:c r="D33" t="inlineStr">
         <x:is>
@@ -1592,10 +1724,10 @@
         </x:is>
       </x:c>
       <x:c r="E33" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F33" s="2" t="n">
-        <x:v>112</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G33" t="inlineStr">
         <x:is>
@@ -1606,6 +1738,12 @@
         <x:is>
           <x:t xml:space="preserve">#387274</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I33" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J33" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1619,10 +1757,8 @@
           <x:t xml:space="preserve">single_sofa_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C34" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·07</x:t>
-        </x:is>
+      <x:c r="C34" t="str">
+        <x:v>单人沙发·07</x:v>
       </x:c>
       <x:c r="D34" t="inlineStr">
         <x:is>
@@ -1630,10 +1766,10 @@
         </x:is>
       </x:c>
       <x:c r="E34" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F34" s="2" t="n">
-        <x:v>113</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G34" t="inlineStr">
         <x:is>
@@ -1644,6 +1780,12 @@
         <x:is>
           <x:t xml:space="preserve">#673212</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I34" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J34" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -1657,10 +1799,8 @@
           <x:t xml:space="preserve">single_sofa_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C35" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·08</x:t>
-        </x:is>
+      <x:c r="C35" t="str">
+        <x:v>单人沙发·08</x:v>
       </x:c>
       <x:c r="D35" t="inlineStr">
         <x:is>
@@ -1668,10 +1808,10 @@
         </x:is>
       </x:c>
       <x:c r="E35" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F35" s="2" t="n">
-        <x:v>114</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G35" t="inlineStr">
         <x:is>
@@ -1682,6 +1822,12 @@
         <x:is>
           <x:t xml:space="preserve">#635D58</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I35" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J35" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1695,10 +1841,8 @@
           <x:t xml:space="preserve">single_sofa_09</x:t>
         </x:is>
       </x:c>
-      <x:c r="C36" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·09</x:t>
-        </x:is>
+      <x:c r="C36" t="str">
+        <x:v>单人沙发·09</x:v>
       </x:c>
       <x:c r="D36" t="inlineStr">
         <x:is>
@@ -1706,10 +1850,10 @@
         </x:is>
       </x:c>
       <x:c r="E36" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F36" s="2" t="n">
-        <x:v>112</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G36" t="inlineStr">
         <x:is>
@@ -1720,6 +1864,12 @@
         <x:is>
           <x:t xml:space="preserve">#C7B391</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I36" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J36" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1733,10 +1883,8 @@
           <x:t xml:space="preserve">single_sofa_10</x:t>
         </x:is>
       </x:c>
-      <x:c r="C37" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·10</x:t>
-        </x:is>
+      <x:c r="C37" t="str">
+        <x:v>单人沙发·10</x:v>
       </x:c>
       <x:c r="D37" t="inlineStr">
         <x:is>
@@ -1744,10 +1892,10 @@
         </x:is>
       </x:c>
       <x:c r="E37" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F37" s="2" t="n">
-        <x:v>111</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G37" t="inlineStr">
         <x:is>
@@ -1758,6 +1906,12 @@
         <x:is>
           <x:t xml:space="preserve">#C08883</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I37" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J37" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -1771,10 +1925,8 @@
           <x:t xml:space="preserve">single_sofa_11</x:t>
         </x:is>
       </x:c>
-      <x:c r="C38" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·11</x:t>
-        </x:is>
+      <x:c r="C38" t="str">
+        <x:v>单人沙发·11</x:v>
       </x:c>
       <x:c r="D38" t="inlineStr">
         <x:is>
@@ -1782,10 +1934,10 @@
         </x:is>
       </x:c>
       <x:c r="E38" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F38" s="2" t="n">
-        <x:v>112</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G38" t="inlineStr">
         <x:is>
@@ -1796,6 +1948,12 @@
         <x:is>
           <x:t xml:space="preserve">#A24A12</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I38" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J38" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -1809,10 +1967,8 @@
           <x:t xml:space="preserve">single_sofa_12</x:t>
         </x:is>
       </x:c>
-      <x:c r="C39" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人沙发·12</x:t>
-        </x:is>
+      <x:c r="C39" t="str">
+        <x:v>单人沙发·12</x:v>
       </x:c>
       <x:c r="D39" t="inlineStr">
         <x:is>
@@ -1820,10 +1976,10 @@
         </x:is>
       </x:c>
       <x:c r="E39" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F39" s="2" t="n">
-        <x:v>110</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G39" t="inlineStr">
         <x:is>
@@ -1834,6 +1990,12 @@
         <x:is>
           <x:t xml:space="preserve">#2A2928</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I39" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J39" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -1847,10 +2009,8 @@
           <x:t xml:space="preserve">armchair_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C40" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">扶手椅·01</x:t>
-        </x:is>
+      <x:c r="C40" t="str">
+        <x:v>扶手椅·01</x:v>
       </x:c>
       <x:c r="D40" t="inlineStr">
         <x:is>
@@ -1858,10 +2018,10 @@
         </x:is>
       </x:c>
       <x:c r="E40" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F40" s="2" t="n">
-        <x:v>114</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G40" t="inlineStr">
         <x:is>
@@ -1872,6 +2032,12 @@
         <x:is>
           <x:t xml:space="preserve">#97211E</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I40" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J40" t="n">
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -1885,10 +2051,8 @@
           <x:t xml:space="preserve">cactus_lamp_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C41" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">仙人掌灯·04</x:t>
-        </x:is>
+      <x:c r="C41" t="str">
+        <x:v>仙人掌灯·04</x:v>
       </x:c>
       <x:c r="D41" t="inlineStr">
         <x:is>
@@ -1896,7 +2060,7 @@
         </x:is>
       </x:c>
       <x:c r="E41" s="2" t="n">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F41" s="2" t="n">
         <x:v>70</x:v>
@@ -1911,6 +2075,12 @@
           <x:t xml:space="preserve">#8A7C58</x:t>
         </x:is>
       </x:c>
+      <x:c r="I41" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J41" t="n">
+        <x:v>105</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="inlineStr">
@@ -1923,10 +2093,8 @@
           <x:t xml:space="preserve">cactus_lamp_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C42" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">仙人掌灯·05</x:t>
-        </x:is>
+      <x:c r="C42" t="str">
+        <x:v>仙人掌灯·05</x:v>
       </x:c>
       <x:c r="D42" t="inlineStr">
         <x:is>
@@ -1934,7 +2102,7 @@
         </x:is>
       </x:c>
       <x:c r="E42" s="2" t="n">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F42" s="2" t="n">
         <x:v>70</x:v>
@@ -1949,6 +2117,12 @@
           <x:t xml:space="preserve">#7C6C63</x:t>
         </x:is>
       </x:c>
+      <x:c r="I42" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J42" t="n">
+        <x:v>105</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="inlineStr">
@@ -1961,10 +2135,8 @@
           <x:t xml:space="preserve">cactus_lamp_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C43" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">仙人掌灯·06</x:t>
-        </x:is>
+      <x:c r="C43" t="str">
+        <x:v>仙人掌灯·06</x:v>
       </x:c>
       <x:c r="D43" t="inlineStr">
         <x:is>
@@ -1972,7 +2144,7 @@
         </x:is>
       </x:c>
       <x:c r="E43" s="2" t="n">
-        <x:v>38</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F43" s="2" t="n">
         <x:v>70</x:v>
@@ -1987,6 +2159,12 @@
           <x:t xml:space="preserve">#A1848B</x:t>
         </x:is>
       </x:c>
+      <x:c r="I43" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J43" t="n">
+        <x:v>105</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="inlineStr">
@@ -1999,10 +2177,8 @@
           <x:t xml:space="preserve">cactus_lamp_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">仙人掌灯·07</x:t>
-        </x:is>
+      <x:c r="C44" t="str">
+        <x:v>仙人掌灯·07</x:v>
       </x:c>
       <x:c r="D44" t="inlineStr">
         <x:is>
@@ -2010,7 +2186,7 @@
         </x:is>
       </x:c>
       <x:c r="E44" s="2" t="n">
-        <x:v>28</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F44" s="2" t="n">
         <x:v>70</x:v>
@@ -2025,6 +2201,12 @@
           <x:t xml:space="preserve">#627A64</x:t>
         </x:is>
       </x:c>
+      <x:c r="I44" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J44" t="n">
+        <x:v>105</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="inlineStr">
@@ -2037,10 +2219,8 @@
           <x:t xml:space="preserve">cactus_lamp_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">仙人掌灯·08</x:t>
-        </x:is>
+      <x:c r="C45" t="str">
+        <x:v>仙人掌灯·08</x:v>
       </x:c>
       <x:c r="D45" t="inlineStr">
         <x:is>
@@ -2048,7 +2228,7 @@
         </x:is>
       </x:c>
       <x:c r="E45" s="2" t="n">
-        <x:v>28</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F45" s="2" t="n">
         <x:v>70</x:v>
@@ -2063,6 +2243,12 @@
           <x:t xml:space="preserve">#4F6455</x:t>
         </x:is>
       </x:c>
+      <x:c r="I45" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="J45" t="n">
+        <x:v>105</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="inlineStr">
@@ -2075,10 +2261,8 @@
           <x:t xml:space="preserve">hanging_plant_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C46" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·01</x:t>
-        </x:is>
+      <x:c r="C46" t="str">
+        <x:v>悬挂绿植·01</x:v>
       </x:c>
       <x:c r="D46" t="inlineStr">
         <x:is>
@@ -2086,10 +2270,10 @@
         </x:is>
       </x:c>
       <x:c r="E46" s="2" t="n">
-        <x:v>54</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F46" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G46" t="inlineStr">
         <x:is>
@@ -2100,6 +2284,12 @@
         <x:is>
           <x:t xml:space="preserve">#AFAE7C</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I46" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J46" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -2113,10 +2303,8 @@
           <x:t xml:space="preserve">hanging_plant_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C47" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·03</x:t>
-        </x:is>
+      <x:c r="C47" t="str">
+        <x:v>悬挂绿植·03</x:v>
       </x:c>
       <x:c r="D47" t="inlineStr">
         <x:is>
@@ -2124,10 +2312,10 @@
         </x:is>
       </x:c>
       <x:c r="E47" s="2" t="n">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F47" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G47" t="inlineStr">
         <x:is>
@@ -2138,6 +2326,12 @@
         <x:is>
           <x:t xml:space="preserve">#98A187</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I47" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J47" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -2151,10 +2345,8 @@
           <x:t xml:space="preserve">hanging_plant_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C48" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·06</x:t>
-        </x:is>
+      <x:c r="C48" t="str">
+        <x:v>悬挂绿植·06</x:v>
       </x:c>
       <x:c r="D48" t="inlineStr">
         <x:is>
@@ -2162,10 +2354,10 @@
         </x:is>
       </x:c>
       <x:c r="E48" s="2" t="n">
-        <x:v>52</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F48" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G48" t="inlineStr">
         <x:is>
@@ -2176,6 +2368,12 @@
         <x:is>
           <x:t xml:space="preserve">#93988E</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I48" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J48" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -2189,10 +2387,8 @@
           <x:t xml:space="preserve">hanging_plant_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C49" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·07</x:t>
-        </x:is>
+      <x:c r="C49" t="str">
+        <x:v>悬挂绿植·07</x:v>
       </x:c>
       <x:c r="D49" t="inlineStr">
         <x:is>
@@ -2200,10 +2396,10 @@
         </x:is>
       </x:c>
       <x:c r="E49" s="2" t="n">
-        <x:v>53</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F49" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G49" t="inlineStr">
         <x:is>
@@ -2214,6 +2410,12 @@
         <x:is>
           <x:t xml:space="preserve">#A8A97E</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I49" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J49" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -2227,10 +2429,8 @@
           <x:t xml:space="preserve">hanging_plant_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·08</x:t>
-        </x:is>
+      <x:c r="C50" t="str">
+        <x:v>悬挂绿植·08</x:v>
       </x:c>
       <x:c r="D50" t="inlineStr">
         <x:is>
@@ -2238,10 +2438,10 @@
         </x:is>
       </x:c>
       <x:c r="E50" s="2" t="n">
-        <x:v>50</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F50" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G50" t="inlineStr">
         <x:is>
@@ -2252,6 +2452,12 @@
         <x:is>
           <x:t xml:space="preserve">#C2BB88</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I50" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J50" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -2265,10 +2471,8 @@
           <x:t xml:space="preserve">hanging_plant_09</x:t>
         </x:is>
       </x:c>
-      <x:c r="C51" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·09</x:t>
-        </x:is>
+      <x:c r="C51" t="str">
+        <x:v>悬挂绿植·09</x:v>
       </x:c>
       <x:c r="D51" t="inlineStr">
         <x:is>
@@ -2276,10 +2480,10 @@
         </x:is>
       </x:c>
       <x:c r="E51" s="2" t="n">
-        <x:v>44</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F51" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G51" t="inlineStr">
         <x:is>
@@ -2290,6 +2494,12 @@
         <x:is>
           <x:t xml:space="preserve">#BAB47F</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I51" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J51" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -2303,10 +2513,8 @@
           <x:t xml:space="preserve">hanging_plant_11</x:t>
         </x:is>
       </x:c>
-      <x:c r="C52" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·11</x:t>
-        </x:is>
+      <x:c r="C52" t="str">
+        <x:v>悬挂绿植·11</x:v>
       </x:c>
       <x:c r="D52" t="inlineStr">
         <x:is>
@@ -2314,10 +2522,10 @@
         </x:is>
       </x:c>
       <x:c r="E52" s="2" t="n">
-        <x:v>44</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F52" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G52" t="inlineStr">
         <x:is>
@@ -2328,6 +2536,12 @@
         <x:is>
           <x:t xml:space="preserve">#B8A895</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I52" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J52" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -2341,10 +2555,8 @@
           <x:t xml:space="preserve">hanging_plant_12</x:t>
         </x:is>
       </x:c>
-      <x:c r="C53" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·12</x:t>
-        </x:is>
+      <x:c r="C53" t="str">
+        <x:v>悬挂绿植·12</x:v>
       </x:c>
       <x:c r="D53" t="inlineStr">
         <x:is>
@@ -2352,10 +2564,10 @@
         </x:is>
       </x:c>
       <x:c r="E53" s="2" t="n">
-        <x:v>27</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F53" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G53" t="inlineStr">
         <x:is>
@@ -2366,6 +2578,12 @@
         <x:is>
           <x:t xml:space="preserve">#AFAD8B</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I53" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J53" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -2379,10 +2597,8 @@
           <x:t xml:space="preserve">hanging_plant_13</x:t>
         </x:is>
       </x:c>
-      <x:c r="C54" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·13</x:t>
-        </x:is>
+      <x:c r="C54" t="str">
+        <x:v>悬挂绿植·13</x:v>
       </x:c>
       <x:c r="D54" t="inlineStr">
         <x:is>
@@ -2390,10 +2606,10 @@
         </x:is>
       </x:c>
       <x:c r="E54" s="2" t="n">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F54" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G54" t="inlineStr">
         <x:is>
@@ -2404,6 +2620,12 @@
         <x:is>
           <x:t xml:space="preserve">#AFB789</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I54" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J54" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -2417,10 +2639,8 @@
           <x:t xml:space="preserve">hanging_plant_14</x:t>
         </x:is>
       </x:c>
-      <x:c r="C55" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·14</x:t>
-        </x:is>
+      <x:c r="C55" t="str">
+        <x:v>悬挂绿植·14</x:v>
       </x:c>
       <x:c r="D55" t="inlineStr">
         <x:is>
@@ -2428,10 +2648,10 @@
         </x:is>
       </x:c>
       <x:c r="E55" s="2" t="n">
-        <x:v>45</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F55" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G55" t="inlineStr">
         <x:is>
@@ -2442,6 +2662,12 @@
         <x:is>
           <x:t xml:space="preserve">#9CA57F</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I55" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J55" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -2455,10 +2681,8 @@
           <x:t xml:space="preserve">hanging_plant_15</x:t>
         </x:is>
       </x:c>
-      <x:c r="C56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·15</x:t>
-        </x:is>
+      <x:c r="C56" t="str">
+        <x:v>悬挂绿植·15</x:v>
       </x:c>
       <x:c r="D56" t="inlineStr">
         <x:is>
@@ -2466,10 +2690,10 @@
         </x:is>
       </x:c>
       <x:c r="E56" s="2" t="n">
-        <x:v>48</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F56" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G56" t="inlineStr">
         <x:is>
@@ -2480,6 +2704,12 @@
         <x:is>
           <x:t xml:space="preserve">#AAA191</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I56" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J56" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -2493,10 +2723,8 @@
           <x:t xml:space="preserve">hanging_plant_16</x:t>
         </x:is>
       </x:c>
-      <x:c r="C57" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·16</x:t>
-        </x:is>
+      <x:c r="C57" t="str">
+        <x:v>悬挂绿植·16</x:v>
       </x:c>
       <x:c r="D57" t="inlineStr">
         <x:is>
@@ -2504,10 +2732,10 @@
         </x:is>
       </x:c>
       <x:c r="E57" s="2" t="n">
-        <x:v>45</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F57" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G57" t="inlineStr">
         <x:is>
@@ -2518,6 +2746,12 @@
         <x:is>
           <x:t xml:space="preserve">#9AA380</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I57" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J57" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -2531,10 +2765,8 @@
           <x:t xml:space="preserve">hanging_plant_17</x:t>
         </x:is>
       </x:c>
-      <x:c r="C58" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·17</x:t>
-        </x:is>
+      <x:c r="C58" t="str">
+        <x:v>悬挂绿植·17</x:v>
       </x:c>
       <x:c r="D58" t="inlineStr">
         <x:is>
@@ -2542,10 +2774,10 @@
         </x:is>
       </x:c>
       <x:c r="E58" s="2" t="n">
-        <x:v>42</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F58" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G58" t="inlineStr">
         <x:is>
@@ -2556,6 +2788,12 @@
         <x:is>
           <x:t xml:space="preserve">#D3D09B</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I58" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J58" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -2569,10 +2807,8 @@
           <x:t xml:space="preserve">hanging_plant_18</x:t>
         </x:is>
       </x:c>
-      <x:c r="C59" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·18</x:t>
-        </x:is>
+      <x:c r="C59" t="str">
+        <x:v>悬挂绿植·18</x:v>
       </x:c>
       <x:c r="D59" t="inlineStr">
         <x:is>
@@ -2580,10 +2816,10 @@
         </x:is>
       </x:c>
       <x:c r="E59" s="2" t="n">
-        <x:v>45</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F59" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G59" t="inlineStr">
         <x:is>
@@ -2594,6 +2830,12 @@
         <x:is>
           <x:t xml:space="preserve">#C9B0A5</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I59" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J59" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -2607,10 +2849,8 @@
           <x:t xml:space="preserve">hanging_plant_21</x:t>
         </x:is>
       </x:c>
-      <x:c r="C60" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·21</x:t>
-        </x:is>
+      <x:c r="C60" t="str">
+        <x:v>悬挂绿植·21</x:v>
       </x:c>
       <x:c r="D60" t="inlineStr">
         <x:is>
@@ -2618,10 +2858,10 @@
         </x:is>
       </x:c>
       <x:c r="E60" s="2" t="n">
-        <x:v>36</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F60" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G60" t="inlineStr">
         <x:is>
@@ -2632,6 +2872,12 @@
         <x:is>
           <x:t xml:space="preserve">#A5AB7D</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I60" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J60" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -2645,10 +2891,8 @@
           <x:t xml:space="preserve">hanging_plant_22</x:t>
         </x:is>
       </x:c>
-      <x:c r="C61" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·22</x:t>
-        </x:is>
+      <x:c r="C61" t="str">
+        <x:v>悬挂绿植·22</x:v>
       </x:c>
       <x:c r="D61" t="inlineStr">
         <x:is>
@@ -2656,10 +2900,10 @@
         </x:is>
       </x:c>
       <x:c r="E61" s="2" t="n">
-        <x:v>42</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F61" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G61" t="inlineStr">
         <x:is>
@@ -2670,6 +2914,12 @@
         <x:is>
           <x:t xml:space="preserve">#ADB496</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I61" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J61" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -2683,10 +2933,8 @@
           <x:t xml:space="preserve">hanging_plant_23</x:t>
         </x:is>
       </x:c>
-      <x:c r="C62" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·23</x:t>
-        </x:is>
+      <x:c r="C62" t="str">
+        <x:v>悬挂绿植·23</x:v>
       </x:c>
       <x:c r="D62" t="inlineStr">
         <x:is>
@@ -2694,10 +2942,10 @@
         </x:is>
       </x:c>
       <x:c r="E62" s="2" t="n">
-        <x:v>41</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F62" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G62" t="inlineStr">
         <x:is>
@@ -2708,6 +2956,12 @@
         <x:is>
           <x:t xml:space="preserve">#D6D485</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I62" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J62" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -2721,10 +2975,8 @@
           <x:t xml:space="preserve">hanging_plant_24</x:t>
         </x:is>
       </x:c>
-      <x:c r="C63" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·24</x:t>
-        </x:is>
+      <x:c r="C63" t="str">
+        <x:v>悬挂绿植·24</x:v>
       </x:c>
       <x:c r="D63" t="inlineStr">
         <x:is>
@@ -2732,10 +2984,10 @@
         </x:is>
       </x:c>
       <x:c r="E63" s="2" t="n">
-        <x:v>47</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F63" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G63" t="inlineStr">
         <x:is>
@@ -2746,6 +2998,12 @@
         <x:is>
           <x:t xml:space="preserve">#B5BEA3</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I63" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J63" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -2759,10 +3017,8 @@
           <x:t xml:space="preserve">hanging_plant_30</x:t>
         </x:is>
       </x:c>
-      <x:c r="C64" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·30</x:t>
-        </x:is>
+      <x:c r="C64" t="str">
+        <x:v>悬挂绿植·30</x:v>
       </x:c>
       <x:c r="D64" t="inlineStr">
         <x:is>
@@ -2770,10 +3026,10 @@
         </x:is>
       </x:c>
       <x:c r="E64" s="2" t="n">
-        <x:v>46</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F64" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G64" t="inlineStr">
         <x:is>
@@ -2784,6 +3040,12 @@
         <x:is>
           <x:t xml:space="preserve">#B2AAAE</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I64" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J64" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -2797,10 +3059,8 @@
           <x:t xml:space="preserve">hanging_plant_31</x:t>
         </x:is>
       </x:c>
-      <x:c r="C65" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·31</x:t>
-        </x:is>
+      <x:c r="C65" t="str">
+        <x:v>悬挂绿植·31</x:v>
       </x:c>
       <x:c r="D65" t="inlineStr">
         <x:is>
@@ -2808,10 +3068,10 @@
         </x:is>
       </x:c>
       <x:c r="E65" s="2" t="n">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F65" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G65" t="inlineStr">
         <x:is>
@@ -2822,6 +3082,12 @@
         <x:is>
           <x:t xml:space="preserve">#C3C567</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I65" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J65" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -2835,10 +3101,8 @@
           <x:t xml:space="preserve">hanging_plant_32</x:t>
         </x:is>
       </x:c>
-      <x:c r="C66" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·32</x:t>
-        </x:is>
+      <x:c r="C66" t="str">
+        <x:v>悬挂绿植·32</x:v>
       </x:c>
       <x:c r="D66" t="inlineStr">
         <x:is>
@@ -2846,10 +3110,10 @@
         </x:is>
       </x:c>
       <x:c r="E66" s="2" t="n">
-        <x:v>45</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F66" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G66" t="inlineStr">
         <x:is>
@@ -2860,6 +3124,12 @@
         <x:is>
           <x:t xml:space="preserve">#90A69F</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I66" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J66" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -2873,10 +3143,8 @@
           <x:t xml:space="preserve">hanging_plant_36</x:t>
         </x:is>
       </x:c>
-      <x:c r="C67" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">悬挂绿植·36</x:t>
-        </x:is>
+      <x:c r="C67" t="str">
+        <x:v>悬挂绿植·36</x:v>
       </x:c>
       <x:c r="D67" t="inlineStr">
         <x:is>
@@ -2884,10 +3152,10 @@
         </x:is>
       </x:c>
       <x:c r="E67" s="2" t="n">
-        <x:v>42</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F67" s="2" t="n">
-        <x:v>90</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G67" t="inlineStr">
         <x:is>
@@ -2898,6 +3166,12 @@
         <x:is>
           <x:t xml:space="preserve">#9CB1A9</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I67" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J67" t="n">
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -2911,10 +3185,8 @@
           <x:t xml:space="preserve">landscape_poster_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C68" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">风景海报·02</x:t>
-        </x:is>
+      <x:c r="C68" t="str">
+        <x:v>风景海报·02</x:v>
       </x:c>
       <x:c r="D68" t="inlineStr">
         <x:is>
@@ -2922,7 +3194,7 @@
         </x:is>
       </x:c>
       <x:c r="E68" s="2" t="n">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F68" s="2" t="n">
         <x:v>105</x:v>
@@ -2937,6 +3209,12 @@
           <x:t xml:space="preserve">#9E9F82</x:t>
         </x:is>
       </x:c>
+      <x:c r="I68" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J68" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="inlineStr">
@@ -2949,10 +3227,8 @@
           <x:t xml:space="preserve">landscape_poster_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C69" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">风景海报·03</x:t>
-        </x:is>
+      <x:c r="C69" t="str">
+        <x:v>风景海报·03</x:v>
       </x:c>
       <x:c r="D69" t="inlineStr">
         <x:is>
@@ -2960,7 +3236,7 @@
         </x:is>
       </x:c>
       <x:c r="E69" s="2" t="n">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F69" s="2" t="n">
         <x:v>105</x:v>
@@ -2975,6 +3251,12 @@
           <x:t xml:space="preserve">#CA9263</x:t>
         </x:is>
       </x:c>
+      <x:c r="I69" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J69" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="inlineStr">
@@ -2987,10 +3269,8 @@
           <x:t xml:space="preserve">landscape_poster_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">风景海报·04</x:t>
-        </x:is>
+      <x:c r="C70" t="str">
+        <x:v>风景海报·04</x:v>
       </x:c>
       <x:c r="D70" t="inlineStr">
         <x:is>
@@ -2998,7 +3278,7 @@
         </x:is>
       </x:c>
       <x:c r="E70" s="2" t="n">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F70" s="2" t="n">
         <x:v>105</x:v>
@@ -3013,6 +3293,12 @@
           <x:t xml:space="preserve">#776A84</x:t>
         </x:is>
       </x:c>
+      <x:c r="I70" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J70" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="inlineStr">
@@ -3025,10 +3311,8 @@
           <x:t xml:space="preserve">landscape_poster_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C71" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">风景海报·05</x:t>
-        </x:is>
+      <x:c r="C71" t="str">
+        <x:v>风景海报·05</x:v>
       </x:c>
       <x:c r="D71" t="inlineStr">
         <x:is>
@@ -3036,7 +3320,7 @@
         </x:is>
       </x:c>
       <x:c r="E71" s="2" t="n">
-        <x:v>68</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F71" s="2" t="n">
         <x:v>105</x:v>
@@ -3051,6 +3335,12 @@
           <x:t xml:space="preserve">#90A2AA</x:t>
         </x:is>
       </x:c>
+      <x:c r="I71" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J71" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="inlineStr">
@@ -3063,10 +3353,8 @@
           <x:t xml:space="preserve">landscape_poster_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C72" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">风景海报·06</x:t>
-        </x:is>
+      <x:c r="C72" t="str">
+        <x:v>风景海报·06</x:v>
       </x:c>
       <x:c r="D72" t="inlineStr">
         <x:is>
@@ -3074,7 +3362,7 @@
         </x:is>
       </x:c>
       <x:c r="E72" s="2" t="n">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F72" s="2" t="n">
         <x:v>105</x:v>
@@ -3089,6 +3377,12 @@
           <x:t xml:space="preserve">#D4A19D</x:t>
         </x:is>
       </x:c>
+      <x:c r="I72" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J72" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="inlineStr">
@@ -3101,10 +3395,8 @@
           <x:t xml:space="preserve">landscape_poster_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C73" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">风景海报·07</x:t>
-        </x:is>
+      <x:c r="C73" t="str">
+        <x:v>风景海报·07</x:v>
       </x:c>
       <x:c r="D73" t="inlineStr">
         <x:is>
@@ -3112,7 +3404,7 @@
         </x:is>
       </x:c>
       <x:c r="E73" s="2" t="n">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F73" s="2" t="n">
         <x:v>105</x:v>
@@ -3127,6 +3419,12 @@
           <x:t xml:space="preserve">#9C958D</x:t>
         </x:is>
       </x:c>
+      <x:c r="I73" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J73" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="inlineStr">
@@ -3139,10 +3437,8 @@
           <x:t xml:space="preserve">landscape_poster_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">风景海报·08</x:t>
-        </x:is>
+      <x:c r="C74" t="str">
+        <x:v>风景海报·08</x:v>
       </x:c>
       <x:c r="D74" t="inlineStr">
         <x:is>
@@ -3150,7 +3446,7 @@
         </x:is>
       </x:c>
       <x:c r="E74" s="2" t="n">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F74" s="2" t="n">
         <x:v>105</x:v>
@@ -3165,6 +3461,12 @@
           <x:t xml:space="preserve">#DBA759</x:t>
         </x:is>
       </x:c>
+      <x:c r="I74" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J74" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="inlineStr">
@@ -3177,10 +3479,8 @@
           <x:t xml:space="preserve">landscape_poster_09</x:t>
         </x:is>
       </x:c>
-      <x:c r="C75" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">风景海报·09</x:t>
-        </x:is>
+      <x:c r="C75" t="str">
+        <x:v>风景海报·09</x:v>
       </x:c>
       <x:c r="D75" t="inlineStr">
         <x:is>
@@ -3188,7 +3488,7 @@
         </x:is>
       </x:c>
       <x:c r="E75" s="2" t="n">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F75" s="2" t="n">
         <x:v>105</x:v>
@@ -3203,6 +3503,12 @@
           <x:t xml:space="preserve">#457273</x:t>
         </x:is>
       </x:c>
+      <x:c r="I75" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J75" t="n">
+        <x:v>135</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="inlineStr">
@@ -3215,10 +3521,8 @@
           <x:t xml:space="preserve">lava_lamp_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C76" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">熔岩灯·01</x:t>
-        </x:is>
+      <x:c r="C76" t="str">
+        <x:v>熔岩灯·01</x:v>
       </x:c>
       <x:c r="D76" t="inlineStr">
         <x:is>
@@ -3226,7 +3530,7 @@
         </x:is>
       </x:c>
       <x:c r="E76" s="2" t="n">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F76" s="2" t="n">
         <x:v>65</x:v>
@@ -3241,6 +3545,12 @@
           <x:t xml:space="preserve">#9D7485</x:t>
         </x:is>
       </x:c>
+      <x:c r="I76" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J76" t="n">
+        <x:v>125</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="inlineStr">
@@ -3253,10 +3563,8 @@
           <x:t xml:space="preserve">lava_lamp_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C77" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">熔岩灯·02</x:t>
-        </x:is>
+      <x:c r="C77" t="str">
+        <x:v>熔岩灯·02</x:v>
       </x:c>
       <x:c r="D77" t="inlineStr">
         <x:is>
@@ -3264,7 +3572,7 @@
         </x:is>
       </x:c>
       <x:c r="E77" s="2" t="n">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F77" s="2" t="n">
         <x:v>65</x:v>
@@ -3279,6 +3587,12 @@
           <x:t xml:space="preserve">#4589A0</x:t>
         </x:is>
       </x:c>
+      <x:c r="I77" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J77" t="n">
+        <x:v>125</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="inlineStr">
@@ -3291,10 +3605,8 @@
           <x:t xml:space="preserve">lava_lamp_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C78" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">熔岩灯·03</x:t>
-        </x:is>
+      <x:c r="C78" t="str">
+        <x:v>熔岩灯·03</x:v>
       </x:c>
       <x:c r="D78" t="inlineStr">
         <x:is>
@@ -3302,7 +3614,7 @@
         </x:is>
       </x:c>
       <x:c r="E78" s="2" t="n">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F78" s="2" t="n">
         <x:v>65</x:v>
@@ -3317,6 +3629,12 @@
           <x:t xml:space="preserve">#A47D46</x:t>
         </x:is>
       </x:c>
+      <x:c r="I78" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J78" t="n">
+        <x:v>125</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="inlineStr">
@@ -3329,10 +3647,8 @@
           <x:t xml:space="preserve">lava_lamp_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C79" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">熔岩灯·04</x:t>
-        </x:is>
+      <x:c r="C79" t="str">
+        <x:v>熔岩灯·04</x:v>
       </x:c>
       <x:c r="D79" t="inlineStr">
         <x:is>
@@ -3340,7 +3656,7 @@
         </x:is>
       </x:c>
       <x:c r="E79" s="2" t="n">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F79" s="2" t="n">
         <x:v>65</x:v>
@@ -3355,6 +3671,12 @@
           <x:t xml:space="preserve">#748E4D</x:t>
         </x:is>
       </x:c>
+      <x:c r="I79" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J79" t="n">
+        <x:v>125</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="inlineStr">
@@ -3367,10 +3689,8 @@
           <x:t xml:space="preserve">lava_lamp_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C80" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">熔岩灯·05</x:t>
-        </x:is>
+      <x:c r="C80" t="str">
+        <x:v>熔岩灯·05</x:v>
       </x:c>
       <x:c r="D80" t="inlineStr">
         <x:is>
@@ -3378,7 +3698,7 @@
         </x:is>
       </x:c>
       <x:c r="E80" s="2" t="n">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F80" s="2" t="n">
         <x:v>65</x:v>
@@ -3393,6 +3713,12 @@
           <x:t xml:space="preserve">#66559E</x:t>
         </x:is>
       </x:c>
+      <x:c r="I80" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J80" t="n">
+        <x:v>125</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="inlineStr">
@@ -3405,10 +3731,8 @@
           <x:t xml:space="preserve">lava_lamp_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C81" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">熔岩灯·06</x:t>
-        </x:is>
+      <x:c r="C81" t="str">
+        <x:v>熔岩灯·06</x:v>
       </x:c>
       <x:c r="D81" t="inlineStr">
         <x:is>
@@ -3416,7 +3740,7 @@
         </x:is>
       </x:c>
       <x:c r="E81" s="2" t="n">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F81" s="2" t="n">
         <x:v>65</x:v>
@@ -3431,6 +3755,12 @@
           <x:t xml:space="preserve">#944F5E</x:t>
         </x:is>
       </x:c>
+      <x:c r="I81" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J81" t="n">
+        <x:v>125</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="inlineStr">
@@ -3443,10 +3773,8 @@
           <x:t xml:space="preserve">lava_lamp_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C82" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">熔岩灯·07</x:t>
-        </x:is>
+      <x:c r="C82" t="str">
+        <x:v>熔岩灯·07</x:v>
       </x:c>
       <x:c r="D82" t="inlineStr">
         <x:is>
@@ -3454,7 +3782,7 @@
         </x:is>
       </x:c>
       <x:c r="E82" s="2" t="n">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F82" s="2" t="n">
         <x:v>65</x:v>
@@ -3469,6 +3797,12 @@
           <x:t xml:space="preserve">#A18547</x:t>
         </x:is>
       </x:c>
+      <x:c r="I82" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J82" t="n">
+        <x:v>125</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="inlineStr">
@@ -3481,10 +3815,8 @@
           <x:t xml:space="preserve">lava_lamp_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C83" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">熔岩灯·08</x:t>
-        </x:is>
+      <x:c r="C83" t="str">
+        <x:v>熔岩灯·08</x:v>
       </x:c>
       <x:c r="D83" t="inlineStr">
         <x:is>
@@ -3492,7 +3824,7 @@
         </x:is>
       </x:c>
       <x:c r="E83" s="2" t="n">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F83" s="2" t="n">
         <x:v>65</x:v>
@@ -3507,6 +3839,12 @@
           <x:t xml:space="preserve">#7898A9</x:t>
         </x:is>
       </x:c>
+      <x:c r="I83" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="J83" t="n">
+        <x:v>125</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="inlineStr">
@@ -3519,10 +3857,8 @@
           <x:t xml:space="preserve">monstera_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C84" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龟背竹·01</x:t>
-        </x:is>
+      <x:c r="C84" t="str">
+        <x:v>龟背竹·01</x:v>
       </x:c>
       <x:c r="D84" t="inlineStr">
         <x:is>
@@ -3530,10 +3866,10 @@
         </x:is>
       </x:c>
       <x:c r="E84" s="2" t="n">
-        <x:v>94</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F84" s="2" t="n">
-        <x:v>145</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G84" t="inlineStr">
         <x:is>
@@ -3544,6 +3880,12 @@
         <x:is>
           <x:t xml:space="preserve">#A3A987</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I84" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="J84" t="n">
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -3557,10 +3899,8 @@
           <x:t xml:space="preserve">monstera_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C85" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龟背竹·02</x:t>
-        </x:is>
+      <x:c r="C85" t="str">
+        <x:v>龟背竹·02</x:v>
       </x:c>
       <x:c r="D85" t="inlineStr">
         <x:is>
@@ -3568,10 +3908,10 @@
         </x:is>
       </x:c>
       <x:c r="E85" s="2" t="n">
-        <x:v>88</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F85" s="2" t="n">
-        <x:v>145</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G85" t="inlineStr">
         <x:is>
@@ -3582,6 +3922,12 @@
         <x:is>
           <x:t xml:space="preserve">#ACB093</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I85" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="J85" t="n">
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -3595,10 +3941,8 @@
           <x:t xml:space="preserve">monstera_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C86" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龟背竹·03</x:t>
-        </x:is>
+      <x:c r="C86" t="str">
+        <x:v>龟背竹·03</x:v>
       </x:c>
       <x:c r="D86" t="inlineStr">
         <x:is>
@@ -3606,10 +3950,10 @@
         </x:is>
       </x:c>
       <x:c r="E86" s="2" t="n">
-        <x:v>95</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F86" s="2" t="n">
-        <x:v>145</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G86" t="inlineStr">
         <x:is>
@@ -3620,6 +3964,12 @@
         <x:is>
           <x:t xml:space="preserve">#6B8075</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I86" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="J86" t="n">
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -3633,10 +3983,8 @@
           <x:t xml:space="preserve">monstera_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C87" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龟背竹·04</x:t>
-        </x:is>
+      <x:c r="C87" t="str">
+        <x:v>龟背竹·04</x:v>
       </x:c>
       <x:c r="D87" t="inlineStr">
         <x:is>
@@ -3644,10 +3992,10 @@
         </x:is>
       </x:c>
       <x:c r="E87" s="2" t="n">
-        <x:v>79</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F87" s="2" t="n">
-        <x:v>145</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G87" t="inlineStr">
         <x:is>
@@ -3658,6 +4006,12 @@
         <x:is>
           <x:t xml:space="preserve">#A6AC8C</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I87" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="J87" t="n">
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -3671,10 +4025,8 @@
           <x:t xml:space="preserve">monstera_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C88" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龟背竹·05</x:t>
-        </x:is>
+      <x:c r="C88" t="str">
+        <x:v>龟背竹·05</x:v>
       </x:c>
       <x:c r="D88" t="inlineStr">
         <x:is>
@@ -3682,10 +4034,10 @@
         </x:is>
       </x:c>
       <x:c r="E88" s="2" t="n">
-        <x:v>94</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F88" s="2" t="n">
-        <x:v>145</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G88" t="inlineStr">
         <x:is>
@@ -3696,6 +4048,12 @@
         <x:is>
           <x:t xml:space="preserve">#CBC79C</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I88" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="J88" t="n">
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -3709,10 +4067,8 @@
           <x:t xml:space="preserve">monstera_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龟背竹·06</x:t>
-        </x:is>
+      <x:c r="C89" t="str">
+        <x:v>龟背竹·06</x:v>
       </x:c>
       <x:c r="D89" t="inlineStr">
         <x:is>
@@ -3720,10 +4076,10 @@
         </x:is>
       </x:c>
       <x:c r="E89" s="2" t="n">
-        <x:v>83</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F89" s="2" t="n">
-        <x:v>145</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G89" t="inlineStr">
         <x:is>
@@ -3734,6 +4090,12 @@
         <x:is>
           <x:t xml:space="preserve">#A2AA93</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I89" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="J89" t="n">
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -3747,10 +4109,8 @@
           <x:t xml:space="preserve">monstera_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C90" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">龟背竹·08</x:t>
-        </x:is>
+      <x:c r="C90" t="str">
+        <x:v>龟背竹·08</x:v>
       </x:c>
       <x:c r="D90" t="inlineStr">
         <x:is>
@@ -3758,10 +4118,10 @@
         </x:is>
       </x:c>
       <x:c r="E90" s="2" t="n">
-        <x:v>63</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F90" s="2" t="n">
-        <x:v>145</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="G90" t="inlineStr">
         <x:is>
@@ -3772,6 +4132,12 @@
         <x:is>
           <x:t xml:space="preserve">#9FA98D</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I90" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="J90" t="n">
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -3785,10 +4151,8 @@
           <x:t xml:space="preserve">orb_decoration_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C91" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">球形摆件·01</x:t>
-        </x:is>
+      <x:c r="C91" t="str">
+        <x:v>球形摆件·01</x:v>
       </x:c>
       <x:c r="D91" t="inlineStr">
         <x:is>
@@ -3796,10 +4160,10 @@
         </x:is>
       </x:c>
       <x:c r="E91" s="2" t="n">
-        <x:v>24</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F91" s="2" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G91" t="inlineStr">
         <x:is>
@@ -3810,6 +4174,12 @@
         <x:is>
           <x:t xml:space="preserve">#8895A1</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I91" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J91" t="n">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -3823,10 +4193,8 @@
           <x:t xml:space="preserve">orb_decoration_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">球形摆件·02</x:t>
-        </x:is>
+      <x:c r="C92" t="str">
+        <x:v>球形摆件·02</x:v>
       </x:c>
       <x:c r="D92" t="inlineStr">
         <x:is>
@@ -3834,10 +4202,10 @@
         </x:is>
       </x:c>
       <x:c r="E92" s="2" t="n">
-        <x:v>23</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F92" s="2" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G92" t="inlineStr">
         <x:is>
@@ -3848,6 +4216,12 @@
         <x:is>
           <x:t xml:space="preserve">#959C92</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I92" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J92" t="n">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -3861,10 +4235,8 @@
           <x:t xml:space="preserve">orb_decoration_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C93" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">球形摆件·03</x:t>
-        </x:is>
+      <x:c r="C93" t="str">
+        <x:v>球形摆件·03</x:v>
       </x:c>
       <x:c r="D93" t="inlineStr">
         <x:is>
@@ -3872,10 +4244,10 @@
         </x:is>
       </x:c>
       <x:c r="E93" s="2" t="n">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F93" s="2" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G93" t="inlineStr">
         <x:is>
@@ -3886,6 +4258,12 @@
         <x:is>
           <x:t xml:space="preserve">#A2A598</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I93" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J93" t="n">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -3899,10 +4277,8 @@
           <x:t xml:space="preserve">orb_decoration_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C94" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">球形摆件·04</x:t>
-        </x:is>
+      <x:c r="C94" t="str">
+        <x:v>球形摆件·04</x:v>
       </x:c>
       <x:c r="D94" t="inlineStr">
         <x:is>
@@ -3910,10 +4286,10 @@
         </x:is>
       </x:c>
       <x:c r="E94" s="2" t="n">
-        <x:v>24</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F94" s="2" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G94" t="inlineStr">
         <x:is>
@@ -3924,6 +4300,12 @@
         <x:is>
           <x:t xml:space="preserve">#9B9E91</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I94" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J94" t="n">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -3937,10 +4319,8 @@
           <x:t xml:space="preserve">orb_decoration_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C95" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">球形摆件·05</x:t>
-        </x:is>
+      <x:c r="C95" t="str">
+        <x:v>球形摆件·05</x:v>
       </x:c>
       <x:c r="D95" t="inlineStr">
         <x:is>
@@ -3948,10 +4328,10 @@
         </x:is>
       </x:c>
       <x:c r="E95" s="2" t="n">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F95" s="2" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G95" t="inlineStr">
         <x:is>
@@ -3962,6 +4342,12 @@
         <x:is>
           <x:t xml:space="preserve">#B6A2A9</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I95" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J95" t="n">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -3975,10 +4361,8 @@
           <x:t xml:space="preserve">orb_decoration_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C96" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">球形摆件·06</x:t>
-        </x:is>
+      <x:c r="C96" t="str">
+        <x:v>球形摆件·06</x:v>
       </x:c>
       <x:c r="D96" t="inlineStr">
         <x:is>
@@ -3986,10 +4370,10 @@
         </x:is>
       </x:c>
       <x:c r="E96" s="2" t="n">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F96" s="2" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G96" t="inlineStr">
         <x:is>
@@ -4000,6 +4384,12 @@
         <x:is>
           <x:t xml:space="preserve">#A2A6A7</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I96" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J96" t="n">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -4013,10 +4403,8 @@
           <x:t xml:space="preserve">orb_decoration_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C97" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">球形摆件·07</x:t>
-        </x:is>
+      <x:c r="C97" t="str">
+        <x:v>球形摆件·07</x:v>
       </x:c>
       <x:c r="D97" t="inlineStr">
         <x:is>
@@ -4024,10 +4412,10 @@
         </x:is>
       </x:c>
       <x:c r="E97" s="2" t="n">
-        <x:v>22</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F97" s="2" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G97" t="inlineStr">
         <x:is>
@@ -4038,6 +4426,12 @@
         <x:is>
           <x:t xml:space="preserve">#A09F97</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I97" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J97" t="n">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -4051,10 +4445,8 @@
           <x:t xml:space="preserve">orb_decoration_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">球形摆件·08</x:t>
-        </x:is>
+      <x:c r="C98" t="str">
+        <x:v>球形摆件·08</x:v>
       </x:c>
       <x:c r="D98" t="inlineStr">
         <x:is>
@@ -4062,10 +4454,10 @@
         </x:is>
       </x:c>
       <x:c r="E98" s="2" t="n">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F98" s="2" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G98" t="inlineStr">
         <x:is>
@@ -4076,6 +4468,12 @@
         <x:is>
           <x:t xml:space="preserve">#9AA095</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I98" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J98" t="n">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -4089,10 +4487,8 @@
           <x:t xml:space="preserve">orb_decoration_09</x:t>
         </x:is>
       </x:c>
-      <x:c r="C99" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">球形摆件·09</x:t>
-        </x:is>
+      <x:c r="C99" t="str">
+        <x:v>球形摆件·09</x:v>
       </x:c>
       <x:c r="D99" t="inlineStr">
         <x:is>
@@ -4100,10 +4496,10 @@
         </x:is>
       </x:c>
       <x:c r="E99" s="2" t="n">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F99" s="2" t="n">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G99" t="inlineStr">
         <x:is>
@@ -4114,6 +4510,12 @@
         <x:is>
           <x:t xml:space="preserve">#99A09B</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I99" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J99" t="n">
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -4127,10 +4529,8 @@
           <x:t xml:space="preserve">potted_plant_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C100" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">盆栽植物·01</x:t>
-        </x:is>
+      <x:c r="C100" t="str">
+        <x:v>盆栽植物·01</x:v>
       </x:c>
       <x:c r="D100" t="inlineStr">
         <x:is>
@@ -4138,10 +4538,10 @@
         </x:is>
       </x:c>
       <x:c r="E100" s="2" t="n">
-        <x:v>41</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F100" s="2" t="n">
-        <x:v>95</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G100" t="inlineStr">
         <x:is>
@@ -4152,6 +4552,12 @@
         <x:is>
           <x:t xml:space="preserve">#AEAC7F</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I100" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J100" t="n">
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -4165,10 +4571,8 @@
           <x:t xml:space="preserve">potted_plant_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">盆栽植物·02</x:t>
-        </x:is>
+      <x:c r="C101" t="str">
+        <x:v>盆栽植物·02</x:v>
       </x:c>
       <x:c r="D101" t="inlineStr">
         <x:is>
@@ -4176,10 +4580,10 @@
         </x:is>
       </x:c>
       <x:c r="E101" s="2" t="n">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F101" s="2" t="n">
-        <x:v>95</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G101" t="inlineStr">
         <x:is>
@@ -4190,6 +4594,12 @@
         <x:is>
           <x:t xml:space="preserve">#CABE8B</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I101" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J101" t="n">
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -4203,10 +4613,8 @@
           <x:t xml:space="preserve">potted_plant_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C102" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">盆栽植物·03</x:t>
-        </x:is>
+      <x:c r="C102" t="str">
+        <x:v>盆栽植物·03</x:v>
       </x:c>
       <x:c r="D102" t="inlineStr">
         <x:is>
@@ -4214,10 +4622,10 @@
         </x:is>
       </x:c>
       <x:c r="E102" s="2" t="n">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F102" s="2" t="n">
-        <x:v>95</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G102" t="inlineStr">
         <x:is>
@@ -4228,6 +4636,12 @@
         <x:is>
           <x:t xml:space="preserve">#DBBF85</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I102" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J102" t="n">
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -4241,10 +4655,8 @@
           <x:t xml:space="preserve">potted_plant_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C103" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">盆栽植物·04</x:t>
-        </x:is>
+      <x:c r="C103" t="str">
+        <x:v>盆栽植物·04</x:v>
       </x:c>
       <x:c r="D103" t="inlineStr">
         <x:is>
@@ -4252,10 +4664,10 @@
         </x:is>
       </x:c>
       <x:c r="E103" s="2" t="n">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F103" s="2" t="n">
-        <x:v>95</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G103" t="inlineStr">
         <x:is>
@@ -4266,6 +4678,12 @@
         <x:is>
           <x:t xml:space="preserve">#879B91</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I103" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J103" t="n">
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -4279,10 +4697,8 @@
           <x:t xml:space="preserve">potted_plant_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C104" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">盆栽植物·06</x:t>
-        </x:is>
+      <x:c r="C104" t="str">
+        <x:v>盆栽植物·06</x:v>
       </x:c>
       <x:c r="D104" t="inlineStr">
         <x:is>
@@ -4290,10 +4706,10 @@
         </x:is>
       </x:c>
       <x:c r="E104" s="2" t="n">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F104" s="2" t="n">
-        <x:v>95</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="G104" t="inlineStr">
         <x:is>
@@ -4304,6 +4720,12 @@
         <x:is>
           <x:t xml:space="preserve">#A1AA95</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I104" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J104" t="n">
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -4317,10 +4739,8 @@
           <x:t xml:space="preserve">round_rug_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C105" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯·01</x:t>
-        </x:is>
+      <x:c r="C105" t="str">
+        <x:v>圆形地毯·01</x:v>
       </x:c>
       <x:c r="D105" t="inlineStr">
         <x:is>
@@ -4328,10 +4748,10 @@
         </x:is>
       </x:c>
       <x:c r="E105" s="2" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F105" s="2" t="n">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G105" t="inlineStr">
         <x:is>
@@ -4342,6 +4762,12 @@
         <x:is>
           <x:t xml:space="preserve">#92A8C3</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I105" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J105" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -4355,10 +4781,8 @@
           <x:t xml:space="preserve">round_rug_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C106" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯·02</x:t>
-        </x:is>
+      <x:c r="C106" t="str">
+        <x:v>圆形地毯·02</x:v>
       </x:c>
       <x:c r="D106" t="inlineStr">
         <x:is>
@@ -4366,10 +4790,10 @@
         </x:is>
       </x:c>
       <x:c r="E106" s="2" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F106" s="2" t="n">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G106" t="inlineStr">
         <x:is>
@@ -4380,6 +4804,12 @@
         <x:is>
           <x:t xml:space="preserve">#9CBAAA</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I106" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J106" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -4393,10 +4823,8 @@
           <x:t xml:space="preserve">round_rug_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C107" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯·03</x:t>
-        </x:is>
+      <x:c r="C107" t="str">
+        <x:v>圆形地毯·03</x:v>
       </x:c>
       <x:c r="D107" t="inlineStr">
         <x:is>
@@ -4404,10 +4832,10 @@
         </x:is>
       </x:c>
       <x:c r="E107" s="2" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F107" s="2" t="n">
-        <x:v>105</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G107" t="inlineStr">
         <x:is>
@@ -4418,6 +4846,12 @@
         <x:is>
           <x:t xml:space="preserve">#A9BDB2</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I107" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J107" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -4431,10 +4865,8 @@
           <x:t xml:space="preserve">round_rug_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C108" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯·04</x:t>
-        </x:is>
+      <x:c r="C108" t="str">
+        <x:v>圆形地毯·04</x:v>
       </x:c>
       <x:c r="D108" t="inlineStr">
         <x:is>
@@ -4442,10 +4874,10 @@
         </x:is>
       </x:c>
       <x:c r="E108" s="2" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F108" s="2" t="n">
-        <x:v>106</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G108" t="inlineStr">
         <x:is>
@@ -4456,6 +4888,12 @@
         <x:is>
           <x:t xml:space="preserve">#DCA88F</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I108" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J108" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -4469,10 +4907,8 @@
           <x:t xml:space="preserve">round_rug_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C109" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯·05</x:t>
-        </x:is>
+      <x:c r="C109" t="str">
+        <x:v>圆形地毯·05</x:v>
       </x:c>
       <x:c r="D109" t="inlineStr">
         <x:is>
@@ -4480,10 +4916,10 @@
         </x:is>
       </x:c>
       <x:c r="E109" s="2" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F109" s="2" t="n">
-        <x:v>106</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G109" t="inlineStr">
         <x:is>
@@ -4494,6 +4930,12 @@
         <x:is>
           <x:t xml:space="preserve">#718EAF</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I109" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J109" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -4507,10 +4949,8 @@
           <x:t xml:space="preserve">round_rug_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C110" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯·06</x:t>
-        </x:is>
+      <x:c r="C110" t="str">
+        <x:v>圆形地毯·06</x:v>
       </x:c>
       <x:c r="D110" t="inlineStr">
         <x:is>
@@ -4518,10 +4958,10 @@
         </x:is>
       </x:c>
       <x:c r="E110" s="2" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F110" s="2" t="n">
-        <x:v>106</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G110" t="inlineStr">
         <x:is>
@@ -4532,6 +4972,12 @@
         <x:is>
           <x:t xml:space="preserve">#EAD29D</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I110" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J110" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -4545,10 +4991,8 @@
           <x:t xml:space="preserve">round_rug_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C111" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯·07</x:t>
-        </x:is>
+      <x:c r="C111" t="str">
+        <x:v>圆形地毯·07</x:v>
       </x:c>
       <x:c r="D111" t="inlineStr">
         <x:is>
@@ -4556,10 +5000,10 @@
         </x:is>
       </x:c>
       <x:c r="E111" s="2" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F111" s="2" t="n">
-        <x:v>108</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G111" t="inlineStr">
         <x:is>
@@ -4570,6 +5014,12 @@
         <x:is>
           <x:t xml:space="preserve">#C5D8E7</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I111" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J111" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -4583,10 +5033,8 @@
           <x:t xml:space="preserve">round_rug_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C112" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯·08</x:t>
-        </x:is>
+      <x:c r="C112" t="str">
+        <x:v>圆形地毯·08</x:v>
       </x:c>
       <x:c r="D112" t="inlineStr">
         <x:is>
@@ -4594,10 +5042,10 @@
         </x:is>
       </x:c>
       <x:c r="E112" s="2" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F112" s="2" t="n">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G112" t="inlineStr">
         <x:is>
@@ -4608,6 +5056,12 @@
         <x:is>
           <x:t xml:space="preserve">#E7C994</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I112" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J112" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -4621,10 +5075,8 @@
           <x:t xml:space="preserve">round_rug_09</x:t>
         </x:is>
       </x:c>
-      <x:c r="C113" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯·09</x:t>
-        </x:is>
+      <x:c r="C113" t="str">
+        <x:v>圆形地毯·09</x:v>
       </x:c>
       <x:c r="D113" t="inlineStr">
         <x:is>
@@ -4632,10 +5084,10 @@
         </x:is>
       </x:c>
       <x:c r="E113" s="2" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F113" s="2" t="n">
-        <x:v>107</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G113" t="inlineStr">
         <x:is>
@@ -4646,6 +5098,12 @@
         <x:is>
           <x:t xml:space="preserve">#EDD6C3</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I113" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J113" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -4659,10 +5117,8 @@
           <x:t xml:space="preserve">round_rug_10</x:t>
         </x:is>
       </x:c>
-      <x:c r="C114" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">圆形地毯·10</x:t>
-        </x:is>
+      <x:c r="C114" t="str">
+        <x:v>圆形地毯·10</x:v>
       </x:c>
       <x:c r="D114" t="inlineStr">
         <x:is>
@@ -4670,10 +5126,10 @@
         </x:is>
       </x:c>
       <x:c r="E114" s="2" t="n">
-        <x:v>210</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="F114" s="2" t="n">
-        <x:v>110</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G114" t="inlineStr">
         <x:is>
@@ -4684,6 +5140,12 @@
         <x:is>
           <x:t xml:space="preserve">#BDD1E1</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I114" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J114" t="n">
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -4697,10 +5159,8 @@
           <x:t xml:space="preserve">vintage_square_clock_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C115" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古方钟·02</x:t>
-        </x:is>
+      <x:c r="C115" t="str">
+        <x:v>复古方钟·02</x:v>
       </x:c>
       <x:c r="D115" t="inlineStr">
         <x:is>
@@ -4708,10 +5168,10 @@
         </x:is>
       </x:c>
       <x:c r="E115" s="2" t="n">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F115" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G115" t="inlineStr">
         <x:is>
@@ -4722,6 +5182,12 @@
         <x:is>
           <x:t xml:space="preserve">#454332</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I115" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J115" t="n">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -4735,10 +5201,8 @@
           <x:t xml:space="preserve">vintage_square_clock_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C116" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古方钟·03</x:t>
-        </x:is>
+      <x:c r="C116" t="str">
+        <x:v>复古方钟·03</x:v>
       </x:c>
       <x:c r="D116" t="inlineStr">
         <x:is>
@@ -4746,10 +5210,10 @@
         </x:is>
       </x:c>
       <x:c r="E116" s="2" t="n">
-        <x:v>59</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F116" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G116" t="inlineStr">
         <x:is>
@@ -4760,6 +5224,12 @@
         <x:is>
           <x:t xml:space="preserve">#3E403B</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I116" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J116" t="n">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -4773,10 +5243,8 @@
           <x:t xml:space="preserve">vintage_square_clock_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C117" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古方钟·04</x:t>
-        </x:is>
+      <x:c r="C117" t="str">
+        <x:v>复古方钟·04</x:v>
       </x:c>
       <x:c r="D117" t="inlineStr">
         <x:is>
@@ -4784,10 +5252,10 @@
         </x:is>
       </x:c>
       <x:c r="E117" s="2" t="n">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F117" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G117" t="inlineStr">
         <x:is>
@@ -4798,6 +5266,12 @@
         <x:is>
           <x:t xml:space="preserve">#3D3429</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I117" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J117" t="n">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -4811,10 +5285,8 @@
           <x:t xml:space="preserve">vintage_square_clock_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C118" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古方钟·05</x:t>
-        </x:is>
+      <x:c r="C118" t="str">
+        <x:v>复古方钟·05</x:v>
       </x:c>
       <x:c r="D118" t="inlineStr">
         <x:is>
@@ -4822,10 +5294,10 @@
         </x:is>
       </x:c>
       <x:c r="E118" s="2" t="n">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F118" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G118" t="inlineStr">
         <x:is>
@@ -4836,6 +5308,12 @@
         <x:is>
           <x:t xml:space="preserve">#B9A17F</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I118" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J118" t="n">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -4849,10 +5327,8 @@
           <x:t xml:space="preserve">vintage_square_clock_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C119" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古方钟·06</x:t>
-        </x:is>
+      <x:c r="C119" t="str">
+        <x:v>复古方钟·06</x:v>
       </x:c>
       <x:c r="D119" t="inlineStr">
         <x:is>
@@ -4860,10 +5336,10 @@
         </x:is>
       </x:c>
       <x:c r="E119" s="2" t="n">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F119" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G119" t="inlineStr">
         <x:is>
@@ -4874,6 +5350,12 @@
         <x:is>
           <x:t xml:space="preserve">#593F2A</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I119" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J119" t="n">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="120">
@@ -4887,10 +5369,8 @@
           <x:t xml:space="preserve">vintage_square_clock_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C120" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古方钟·07</x:t>
-        </x:is>
+      <x:c r="C120" t="str">
+        <x:v>复古方钟·07</x:v>
       </x:c>
       <x:c r="D120" t="inlineStr">
         <x:is>
@@ -4898,10 +5378,10 @@
         </x:is>
       </x:c>
       <x:c r="E120" s="2" t="n">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F120" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G120" t="inlineStr">
         <x:is>
@@ -4912,6 +5392,12 @@
         <x:is>
           <x:t xml:space="preserve">#3C3B2E</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I120" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J120" t="n">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="121">
@@ -4925,10 +5411,8 @@
           <x:t xml:space="preserve">vintage_square_clock_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C121" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古方钟·08</x:t>
-        </x:is>
+      <x:c r="C121" t="str">
+        <x:v>复古方钟·08</x:v>
       </x:c>
       <x:c r="D121" t="inlineStr">
         <x:is>
@@ -4936,10 +5420,10 @@
         </x:is>
       </x:c>
       <x:c r="E121" s="2" t="n">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F121" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G121" t="inlineStr">
         <x:is>
@@ -4950,6 +5434,12 @@
         <x:is>
           <x:t xml:space="preserve">#623E34</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I121" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J121" t="n">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="122">
@@ -4963,10 +5453,8 @@
           <x:t xml:space="preserve">vintage_square_clock_10</x:t>
         </x:is>
       </x:c>
-      <x:c r="C122" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古方钟·10</x:t>
-        </x:is>
+      <x:c r="C122" t="str">
+        <x:v>复古方钟·10</x:v>
       </x:c>
       <x:c r="D122" t="inlineStr">
         <x:is>
@@ -4974,10 +5462,10 @@
         </x:is>
       </x:c>
       <x:c r="E122" s="2" t="n">
-        <x:v>58</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F122" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G122" t="inlineStr">
         <x:is>
@@ -4988,6 +5476,12 @@
         <x:is>
           <x:t xml:space="preserve">#7F5A36</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I122" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J122" t="n">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="123">
@@ -5001,10 +5495,8 @@
           <x:t xml:space="preserve">vintage_square_clock_11</x:t>
         </x:is>
       </x:c>
-      <x:c r="C123" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古方钟·11</x:t>
-        </x:is>
+      <x:c r="C123" t="str">
+        <x:v>复古方钟·11</x:v>
       </x:c>
       <x:c r="D123" t="inlineStr">
         <x:is>
@@ -5012,10 +5504,10 @@
         </x:is>
       </x:c>
       <x:c r="E123" s="2" t="n">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F123" s="2" t="n">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G123" t="inlineStr">
         <x:is>
@@ -5026,6 +5518,12 @@
         <x:is>
           <x:t xml:space="preserve">#595A4E</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I123" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J123" t="n">
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="124">
@@ -5039,10 +5537,8 @@
           <x:t xml:space="preserve">bed_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C124" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人床·01</x:t>
-        </x:is>
+      <x:c r="C124" t="str">
+        <x:v>单人床·01</x:v>
       </x:c>
       <x:c r="D124" t="inlineStr">
         <x:is>
@@ -5053,7 +5549,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="F124" s="2" t="n">
-        <x:v>149</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G124" t="inlineStr">
         <x:is>
@@ -5064,6 +5560,12 @@
         <x:is>
           <x:t xml:space="preserve">#DECDAF</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I124" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="J124" t="n">
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -5077,10 +5579,8 @@
           <x:t xml:space="preserve">bed_02</x:t>
         </x:is>
       </x:c>
-      <x:c r="C125" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人床·02</x:t>
-        </x:is>
+      <x:c r="C125" t="str">
+        <x:v>单人床·02</x:v>
       </x:c>
       <x:c r="D125" t="inlineStr">
         <x:is>
@@ -5091,7 +5591,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="F125" s="2" t="n">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G125" t="inlineStr">
         <x:is>
@@ -5102,6 +5602,12 @@
         <x:is>
           <x:t xml:space="preserve">#D6CAB4</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I125" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="J125" t="n">
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -5115,10 +5621,8 @@
           <x:t xml:space="preserve">bed_03</x:t>
         </x:is>
       </x:c>
-      <x:c r="C126" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人床·03</x:t>
-        </x:is>
+      <x:c r="C126" t="str">
+        <x:v>单人床·03</x:v>
       </x:c>
       <x:c r="D126" t="inlineStr">
         <x:is>
@@ -5129,7 +5633,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="F126" s="2" t="n">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G126" t="inlineStr">
         <x:is>
@@ -5140,6 +5644,12 @@
         <x:is>
           <x:t xml:space="preserve">#D3BB96</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I126" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="J126" t="n">
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -5153,10 +5663,8 @@
           <x:t xml:space="preserve">bed_04</x:t>
         </x:is>
       </x:c>
-      <x:c r="C127" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人床·04</x:t>
-        </x:is>
+      <x:c r="C127" t="str">
+        <x:v>单人床·04</x:v>
       </x:c>
       <x:c r="D127" t="inlineStr">
         <x:is>
@@ -5167,7 +5675,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="F127" s="2" t="n">
-        <x:v>146</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G127" t="inlineStr">
         <x:is>
@@ -5178,6 +5686,12 @@
         <x:is>
           <x:t xml:space="preserve">#BFA57C</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I127" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="J127" t="n">
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -5191,10 +5705,8 @@
           <x:t xml:space="preserve">bed_05</x:t>
         </x:is>
       </x:c>
-      <x:c r="C128" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">单人床·05</x:t>
-        </x:is>
+      <x:c r="C128" t="str">
+        <x:v>单人床·05</x:v>
       </x:c>
       <x:c r="D128" t="inlineStr">
         <x:is>
@@ -5205,7 +5717,7 @@
         <x:v>220</x:v>
       </x:c>
       <x:c r="F128" s="2" t="n">
-        <x:v>134</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="G128" t="inlineStr">
         <x:is>
@@ -5216,6 +5728,12 @@
         <x:is>
           <x:t xml:space="preserve">#AFBDC7</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I128" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="J128" t="n">
+        <x:v>145</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -5229,10 +5747,8 @@
           <x:t xml:space="preserve">bed_06</x:t>
         </x:is>
       </x:c>
-      <x:c r="C129" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">床头床·01</x:t>
-        </x:is>
+      <x:c r="C129" t="str">
+        <x:v>床头床·01</x:v>
       </x:c>
       <x:c r="D129" t="inlineStr">
         <x:is>
@@ -5243,7 +5759,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="F129" s="2" t="n">
-        <x:v>166</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G129" t="inlineStr">
         <x:is>
@@ -5254,6 +5770,12 @@
         <x:is>
           <x:t xml:space="preserve">#E3D5CA</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I129" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J129" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -5267,10 +5789,8 @@
           <x:t xml:space="preserve">bed_07</x:t>
         </x:is>
       </x:c>
-      <x:c r="C130" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">床头床·02</x:t>
-        </x:is>
+      <x:c r="C130" t="str">
+        <x:v>床头床·02</x:v>
       </x:c>
       <x:c r="D130" t="inlineStr">
         <x:is>
@@ -5281,7 +5801,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="F130" s="2" t="n">
-        <x:v>129</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G130" t="inlineStr">
         <x:is>
@@ -5292,6 +5812,12 @@
         <x:is>
           <x:t xml:space="preserve">#BFAB8C</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I130" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J130" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -5305,10 +5831,8 @@
           <x:t xml:space="preserve">bed_08</x:t>
         </x:is>
       </x:c>
-      <x:c r="C131" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">床头床·03</x:t>
-        </x:is>
+      <x:c r="C131" t="str">
+        <x:v>床头床·03</x:v>
       </x:c>
       <x:c r="D131" t="inlineStr">
         <x:is>
@@ -5319,7 +5843,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="F131" s="2" t="n">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G131" t="inlineStr">
         <x:is>
@@ -5330,6 +5854,12 @@
         <x:is>
           <x:t xml:space="preserve">#BCBBB8</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I131" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J131" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -5343,10 +5873,8 @@
           <x:t xml:space="preserve">bed_09</x:t>
         </x:is>
       </x:c>
-      <x:c r="C132" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">床头床·04</x:t>
-        </x:is>
+      <x:c r="C132" t="str">
+        <x:v>床头床·04</x:v>
       </x:c>
       <x:c r="D132" t="inlineStr">
         <x:is>
@@ -5357,7 +5885,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="F132" s="2" t="n">
-        <x:v>115</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G132" t="inlineStr">
         <x:is>
@@ -5368,6 +5896,12 @@
         <x:is>
           <x:t xml:space="preserve">#B7B2AC</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I132" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J132" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -5381,10 +5915,8 @@
           <x:t xml:space="preserve">bed_10</x:t>
         </x:is>
       </x:c>
-      <x:c r="C133" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">床头床·05</x:t>
-        </x:is>
+      <x:c r="C133" t="str">
+        <x:v>床头床·05</x:v>
       </x:c>
       <x:c r="D133" t="inlineStr">
         <x:is>
@@ -5395,7 +5927,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="F133" s="2" t="n">
-        <x:v>153</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G133" t="inlineStr">
         <x:is>
@@ -5406,6 +5938,12 @@
         <x:is>
           <x:t xml:space="preserve">#E9A089</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I133" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J133" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -5419,10 +5957,8 @@
           <x:t xml:space="preserve">bed_11</x:t>
         </x:is>
       </x:c>
-      <x:c r="C134" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">床头床·06</x:t>
-        </x:is>
+      <x:c r="C134" t="str">
+        <x:v>床头床·06</x:v>
       </x:c>
       <x:c r="D134" t="inlineStr">
         <x:is>
@@ -5433,7 +5969,7 @@
         <x:v>160</x:v>
       </x:c>
       <x:c r="F134" s="2" t="n">
-        <x:v>156</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="G134" t="inlineStr">
         <x:is>
@@ -5444,6 +5980,12 @@
         <x:is>
           <x:t xml:space="preserve">#C8D1D9</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I134" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J134" t="n">
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -5457,10 +5999,8 @@
           <x:t xml:space="preserve">vanity_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C135" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">彩色梳妆台·01</x:t>
-        </x:is>
+      <x:c r="C135" t="str">
+        <x:v>彩色梳妆台·01</x:v>
       </x:c>
       <x:c r="D135" t="inlineStr">
         <x:is>
@@ -5468,10 +6008,10 @@
         </x:is>
       </x:c>
       <x:c r="E135" s="2" t="n">
-        <x:v>125</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F135" s="2" t="n">
-        <x:v>159</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="G135" t="inlineStr">
         <x:is>
@@ -5482,6 +6022,12 @@
         <x:is>
           <x:t xml:space="preserve">#DBBF9E</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I135" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="J135" t="n">
+        <x:v>185</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -5495,10 +6041,8 @@
           <x:t xml:space="preserve">retro_radio_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C136" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古收音机·01</x:t>
-        </x:is>
+      <x:c r="C136" t="str">
+        <x:v>复古收音机·01</x:v>
       </x:c>
       <x:c r="D136" t="inlineStr">
         <x:is>
@@ -5506,10 +6050,10 @@
         </x:is>
       </x:c>
       <x:c r="E136" s="2" t="n">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F136" s="2" t="n">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G136" t="inlineStr">
         <x:is>
@@ -5520,6 +6064,12 @@
         <x:is>
           <x:t xml:space="preserve">#8DA092</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I136" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J136" t="n">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -5533,10 +6083,8 @@
           <x:t xml:space="preserve">music_player_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C137" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">音乐播放器·01</x:t>
-        </x:is>
+      <x:c r="C137" t="str">
+        <x:v>音乐播放器·01</x:v>
       </x:c>
       <x:c r="D137" t="inlineStr">
         <x:is>
@@ -5544,10 +6092,10 @@
         </x:is>
       </x:c>
       <x:c r="E137" s="2" t="n">
-        <x:v>130</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="F137" s="2" t="n">
-        <x:v>101</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="G137" t="inlineStr">
         <x:is>
@@ -5558,6 +6106,12 @@
         <x:is>
           <x:t xml:space="preserve">#BA9A8D</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I137" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J137" t="n">
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -5571,10 +6125,8 @@
           <x:t xml:space="preserve">piano_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C138" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">奶油钢琴·01</x:t>
-        </x:is>
+      <x:c r="C138" t="str">
+        <x:v>奶油钢琴·01</x:v>
       </x:c>
       <x:c r="D138" t="inlineStr">
         <x:is>
@@ -5582,10 +6134,10 @@
         </x:is>
       </x:c>
       <x:c r="E138" s="2" t="n">
-        <x:v>190</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="F138" s="2" t="n">
-        <x:v>184</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="G138" t="inlineStr">
         <x:is>
@@ -5596,6 +6148,12 @@
         <x:is>
           <x:t xml:space="preserve">#858B98</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I138" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="J138" t="n">
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -5609,10 +6167,8 @@
           <x:t xml:space="preserve">flashlight_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C139" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">手电筒·01</x:t>
-        </x:is>
+      <x:c r="C139" t="str">
+        <x:v>手电筒·01</x:v>
       </x:c>
       <x:c r="D139" t="inlineStr">
         <x:is>
@@ -5620,10 +6176,10 @@
         </x:is>
       </x:c>
       <x:c r="E139" s="2" t="n">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F139" s="2" t="n">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G139" t="inlineStr">
         <x:is>
@@ -5634,6 +6190,12 @@
         <x:is>
           <x:t xml:space="preserve">#80A6BA</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I139" t="n">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="J139" t="n">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="140">
@@ -5647,10 +6209,8 @@
           <x:t xml:space="preserve">iron_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C140" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古熨斗·01</x:t>
-        </x:is>
+      <x:c r="C140" t="str">
+        <x:v>复古熨斗·01</x:v>
       </x:c>
       <x:c r="D140" t="inlineStr">
         <x:is>
@@ -5658,10 +6218,10 @@
         </x:is>
       </x:c>
       <x:c r="E140" s="2" t="n">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F140" s="2" t="n">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="G140" t="inlineStr">
         <x:is>
@@ -5672,6 +6232,12 @@
         <x:is>
           <x:t xml:space="preserve">#B2CADB</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I140" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J140" t="n">
+        <x:v>75</x:v>
       </x:c>
     </x:row>
     <x:row r="141">
@@ -5685,10 +6251,8 @@
           <x:t xml:space="preserve">telescope_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C141" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古望远镜·01</x:t>
-        </x:is>
+      <x:c r="C141" t="str">
+        <x:v>复古望远镜·01</x:v>
       </x:c>
       <x:c r="D141" t="inlineStr">
         <x:is>
@@ -5696,10 +6260,10 @@
         </x:is>
       </x:c>
       <x:c r="E141" s="2" t="n">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F141" s="2" t="n">
-        <x:v>74</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G141" t="inlineStr">
         <x:is>
@@ -5710,6 +6274,12 @@
         <x:is>
           <x:t xml:space="preserve">#BEA486</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I141" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="J141" t="n">
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="142">
@@ -5723,10 +6293,8 @@
           <x:t xml:space="preserve">colorful_cabinet_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C142" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">彩色柜子·01</x:t>
-        </x:is>
+      <x:c r="C142" t="str">
+        <x:v>彩色柜子·01</x:v>
       </x:c>
       <x:c r="D142" t="inlineStr">
         <x:is>
@@ -5734,10 +6302,10 @@
         </x:is>
       </x:c>
       <x:c r="E142" s="2" t="n">
-        <x:v>170</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F142" s="2" t="n">
-        <x:v>92</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G142" t="inlineStr">
         <x:is>
@@ -5748,6 +6316,12 @@
         <x:is>
           <x:t xml:space="preserve">#D0C8AC</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I142" t="n">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="J142" t="n">
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -5761,10 +6335,8 @@
           <x:t xml:space="preserve">floor_lamp_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C143" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">艺术落地灯·01</x:t>
-        </x:is>
+      <x:c r="C143" t="str">
+        <x:v>艺术落地灯·01</x:v>
       </x:c>
       <x:c r="D143" t="inlineStr">
         <x:is>
@@ -5772,10 +6344,10 @@
         </x:is>
       </x:c>
       <x:c r="E143" s="2" t="n">
-        <x:v>76</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F143" s="2" t="n">
-        <x:v>165</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="G143" t="inlineStr">
         <x:is>
@@ -5786,6 +6358,12 @@
         <x:is>
           <x:t xml:space="preserve">#B18F5F</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I143" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="J143" t="n">
+        <x:v>215</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -5799,10 +6377,8 @@
           <x:t xml:space="preserve">chalkboard_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C144" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">复古黑板·01</x:t>
-        </x:is>
+      <x:c r="C144" t="str">
+        <x:v>复古黑板·01</x:v>
       </x:c>
       <x:c r="D144" t="inlineStr">
         <x:is>
@@ -5813,7 +6389,7 @@
         <x:v>180</x:v>
       </x:c>
       <x:c r="F144" s="2" t="n">
-        <x:v>132</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="G144" t="inlineStr">
         <x:is>
@@ -5824,6 +6400,12 @@
         <x:is>
           <x:t xml:space="preserve">#C4905C</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I144" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J144" t="n">
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -5837,10 +6419,8 @@
           <x:t xml:space="preserve">macaron_sofa_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C145" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">马卡龙沙发·01</x:t>
-        </x:is>
+      <x:c r="C145" t="str">
+        <x:v>马卡龙沙发·01</x:v>
       </x:c>
       <x:c r="D145" t="inlineStr">
         <x:is>
@@ -5848,10 +6428,10 @@
         </x:is>
       </x:c>
       <x:c r="E145" s="2" t="n">
-        <x:v>180</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="F145" s="2" t="n">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G145" t="inlineStr">
         <x:is>
@@ -5862,6 +6442,12 @@
         <x:is>
           <x:t xml:space="preserve">#BDCECE</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I145" t="n">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="J145" t="n">
+        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -5875,10 +6461,8 @@
           <x:t xml:space="preserve">metronome_01</x:t>
         </x:is>
       </x:c>
-      <x:c r="C146" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">节拍器·01</x:t>
-        </x:is>
+      <x:c r="C146" t="str">
+        <x:v>节拍器·01</x:v>
       </x:c>
       <x:c r="D146" t="inlineStr">
         <x:is>
@@ -5886,7 +6470,7 @@
         </x:is>
       </x:c>
       <x:c r="E146" s="2" t="n">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F146" s="2" t="n">
         <x:v>55</x:v>
@@ -5900,6 +6484,12 @@
         <x:is>
           <x:t xml:space="preserve">#89A1B6</x:t>
         </x:is>
+      </x:c>
+      <x:c r="I146" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="J146" t="n">
+        <x:v>100</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Excel/家具表.xlsx
+++ b/Excel/家具表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具" sheetId="1" r:id="R41c6267c0f8a4dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具" sheetId="1" r:id="R3c458a2154e54295"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -346,6 +346,10 @@
     <x:col min="8" max="8" width="10" customWidth="1"/>
     <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="50" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="50" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="10" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -395,6 +399,18 @@
       <x:c r="J1" t="str">
         <x:v>商店显示高</x:v>
       </x:c>
+      <x:c r="K1" t="str">
+        <x:v>商店列表图</x:v>
+      </x:c>
+      <x:c r="L1" t="str">
+        <x:v>商店详情图</x:v>
+      </x:c>
+      <x:c r="M1" t="str">
+        <x:v>占格列</x:v>
+      </x:c>
+      <x:c r="N1" t="str">
+        <x:v>占格行</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="1" t="inlineStr">
@@ -443,6 +459,18 @@
       <x:c r="J2" t="str">
         <x:v>storeDisplayHeight</x:v>
       </x:c>
+      <x:c r="K2" t="str">
+        <x:v>storeListSprite</x:v>
+      </x:c>
+      <x:c r="L2" t="str">
+        <x:v>storePreviewSprite</x:v>
+      </x:c>
+      <x:c r="M2" t="str">
+        <x:v>cols</x:v>
+      </x:c>
+      <x:c r="N2" t="str">
+        <x:v>rows</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="inlineStr">
@@ -485,6 +513,18 @@
       <x:c r="J3" t="n">
         <x:v>220</x:v>
       </x:c>
+      <x:c r="K3" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/台灯-1.png</x:v>
+      </x:c>
+      <x:c r="L3" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-1.png</x:v>
+      </x:c>
+      <x:c r="M3" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N3" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="inlineStr">
@@ -527,6 +567,18 @@
       <x:c r="J4" t="n">
         <x:v>220</x:v>
       </x:c>
+      <x:c r="K4" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/台灯-2.png</x:v>
+      </x:c>
+      <x:c r="L4" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-2.png</x:v>
+      </x:c>
+      <x:c r="M4" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N4" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" t="inlineStr">
@@ -569,6 +621,18 @@
       <x:c r="J5" t="n">
         <x:v>220</x:v>
       </x:c>
+      <x:c r="K5" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/台灯-3.png</x:v>
+      </x:c>
+      <x:c r="L5" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-3.png</x:v>
+      </x:c>
+      <x:c r="M5" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N5" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" t="inlineStr">
@@ -611,6 +675,18 @@
       <x:c r="J6" t="n">
         <x:v>220</x:v>
       </x:c>
+      <x:c r="K6" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/台灯-4.png</x:v>
+      </x:c>
+      <x:c r="L6" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-4.png</x:v>
+      </x:c>
+      <x:c r="M6" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N6" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" t="inlineStr">
@@ -653,6 +729,18 @@
       <x:c r="J7" t="n">
         <x:v>220</x:v>
       </x:c>
+      <x:c r="K7" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/台灯-5.png</x:v>
+      </x:c>
+      <x:c r="L7" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-5.png</x:v>
+      </x:c>
+      <x:c r="M7" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N7" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" t="inlineStr">
@@ -695,6 +783,18 @@
       <x:c r="J8" t="n">
         <x:v>220</x:v>
       </x:c>
+      <x:c r="K8" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/台灯-6.png</x:v>
+      </x:c>
+      <x:c r="L8" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-6.png</x:v>
+      </x:c>
+      <x:c r="M8" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N8" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" t="inlineStr">
@@ -737,6 +837,14 @@
       <x:c r="J9" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K9" t="str"/>
+      <x:c r="L9" t="str"/>
+      <x:c r="M9" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N9" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="inlineStr">
@@ -779,6 +887,14 @@
       <x:c r="J10" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K10" t="str"/>
+      <x:c r="L10" t="str"/>
+      <x:c r="M10" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N10" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="inlineStr">
@@ -821,6 +937,14 @@
       <x:c r="J11" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K11" t="str"/>
+      <x:c r="L11" t="str"/>
+      <x:c r="M11" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N11" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" t="inlineStr">
@@ -863,6 +987,14 @@
       <x:c r="J12" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K12" t="str"/>
+      <x:c r="L12" t="str"/>
+      <x:c r="M12" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N12" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" t="inlineStr">
@@ -905,6 +1037,14 @@
       <x:c r="J13" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K13" t="str"/>
+      <x:c r="L13" t="str"/>
+      <x:c r="M13" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N13" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" t="inlineStr">
@@ -947,6 +1087,14 @@
       <x:c r="J14" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K14" t="str"/>
+      <x:c r="L14" t="str"/>
+      <x:c r="M14" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N14" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" t="inlineStr">
@@ -989,6 +1137,14 @@
       <x:c r="J15" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K15" t="str"/>
+      <x:c r="L15" t="str"/>
+      <x:c r="M15" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N15" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="inlineStr">
@@ -1031,6 +1187,14 @@
       <x:c r="J16" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K16" t="str"/>
+      <x:c r="L16" t="str"/>
+      <x:c r="M16" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N16" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="inlineStr">
@@ -1073,6 +1237,14 @@
       <x:c r="J17" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K17" t="str"/>
+      <x:c r="L17" t="str"/>
+      <x:c r="M17" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N17" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="inlineStr">
@@ -1115,6 +1287,14 @@
       <x:c r="J18" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K18" t="str"/>
+      <x:c r="L18" t="str"/>
+      <x:c r="M18" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N18" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="inlineStr">
@@ -1157,6 +1337,14 @@
       <x:c r="J19" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K19" t="str"/>
+      <x:c r="L19" t="str"/>
+      <x:c r="M19" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N19" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="inlineStr">
@@ -1199,6 +1387,14 @@
       <x:c r="J20" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K20" t="str"/>
+      <x:c r="L20" t="str"/>
+      <x:c r="M20" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N20" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="inlineStr">
@@ -1241,6 +1437,14 @@
       <x:c r="J21" t="n">
         <x:v>120</x:v>
       </x:c>
+      <x:c r="K21" t="str"/>
+      <x:c r="L21" t="str"/>
+      <x:c r="M21" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N21" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="inlineStr">
@@ -1283,6 +1487,14 @@
       <x:c r="J22" t="n">
         <x:v>120</x:v>
       </x:c>
+      <x:c r="K22" t="str"/>
+      <x:c r="L22" t="str"/>
+      <x:c r="M22" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N22" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="inlineStr">
@@ -1325,6 +1537,14 @@
       <x:c r="J23" t="n">
         <x:v>120</x:v>
       </x:c>
+      <x:c r="K23" t="str"/>
+      <x:c r="L23" t="str"/>
+      <x:c r="M23" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N23" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="inlineStr">
@@ -1367,6 +1587,14 @@
       <x:c r="J24" t="n">
         <x:v>120</x:v>
       </x:c>
+      <x:c r="K24" t="str"/>
+      <x:c r="L24" t="str"/>
+      <x:c r="M24" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N24" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="inlineStr">
@@ -1409,6 +1637,14 @@
       <x:c r="J25" t="n">
         <x:v>120</x:v>
       </x:c>
+      <x:c r="K25" t="str"/>
+      <x:c r="L25" t="str"/>
+      <x:c r="M25" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N25" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="inlineStr">
@@ -1451,6 +1687,14 @@
       <x:c r="J26" t="n">
         <x:v>120</x:v>
       </x:c>
+      <x:c r="K26" t="str"/>
+      <x:c r="L26" t="str"/>
+      <x:c r="M26" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N26" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="inlineStr">
@@ -1493,6 +1737,14 @@
       <x:c r="J27" t="n">
         <x:v>120</x:v>
       </x:c>
+      <x:c r="K27" t="str"/>
+      <x:c r="L27" t="str"/>
+      <x:c r="M27" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N27" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="inlineStr">
@@ -1535,6 +1787,14 @@
       <x:c r="J28" t="n">
         <x:v>120</x:v>
       </x:c>
+      <x:c r="K28" t="str"/>
+      <x:c r="L28" t="str"/>
+      <x:c r="M28" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N28" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="inlineStr">
@@ -1577,6 +1837,18 @@
       <x:c r="J29" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K29" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_10 3.png</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_10 2.png</x:v>
+      </x:c>
+      <x:c r="M29" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N29" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="inlineStr">
@@ -1619,6 +1891,18 @@
       <x:c r="J30" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K30" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_04 3.png</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_04 2.png</x:v>
+      </x:c>
+      <x:c r="M30" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N30" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="inlineStr">
@@ -1661,6 +1945,18 @@
       <x:c r="J31" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K31" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_09 3.png</x:v>
+      </x:c>
+      <x:c r="L31" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_09 2.png</x:v>
+      </x:c>
+      <x:c r="M31" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N31" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="inlineStr">
@@ -1703,6 +1999,18 @@
       <x:c r="J32" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K32" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_05 3.png</x:v>
+      </x:c>
+      <x:c r="L32" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_05 2.png</x:v>
+      </x:c>
+      <x:c r="M32" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N32" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="inlineStr">
@@ -1745,6 +2053,18 @@
       <x:c r="J33" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K33" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_06 3.png</x:v>
+      </x:c>
+      <x:c r="L33" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_06 2.png</x:v>
+      </x:c>
+      <x:c r="M33" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N33" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="inlineStr">
@@ -1787,6 +2107,18 @@
       <x:c r="J34" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K34" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_07 3.png</x:v>
+      </x:c>
+      <x:c r="L34" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_07 2.png</x:v>
+      </x:c>
+      <x:c r="M34" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N34" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="inlineStr">
@@ -1829,6 +2161,18 @@
       <x:c r="J35" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K35" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_08 3.png</x:v>
+      </x:c>
+      <x:c r="L35" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_08 2.png</x:v>
+      </x:c>
+      <x:c r="M35" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N35" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="inlineStr">
@@ -1871,6 +2215,18 @@
       <x:c r="J36" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K36" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_01 3.png</x:v>
+      </x:c>
+      <x:c r="L36" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_01 2.png</x:v>
+      </x:c>
+      <x:c r="M36" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N36" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="inlineStr">
@@ -1913,6 +2269,18 @@
       <x:c r="J37" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K37" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_02 3.png</x:v>
+      </x:c>
+      <x:c r="L37" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_02 2.png</x:v>
+      </x:c>
+      <x:c r="M37" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N37" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="inlineStr">
@@ -1955,6 +2323,18 @@
       <x:c r="J38" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K38" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_11 3.png</x:v>
+      </x:c>
+      <x:c r="L38" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_11 2.png</x:v>
+      </x:c>
+      <x:c r="M38" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N38" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="inlineStr">
@@ -1997,6 +2377,18 @@
       <x:c r="J39" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K39" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_12 3.png</x:v>
+      </x:c>
+      <x:c r="L39" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_12 2.png</x:v>
+      </x:c>
+      <x:c r="M39" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N39" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" t="inlineStr">
@@ -2039,6 +2431,18 @@
       <x:c r="J40" t="n">
         <x:v>160</x:v>
       </x:c>
+      <x:c r="K40" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/armchair_03 3.png</x:v>
+      </x:c>
+      <x:c r="L40" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_03 2.png</x:v>
+      </x:c>
+      <x:c r="M40" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N40" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" t="inlineStr">
@@ -2081,6 +2485,14 @@
       <x:c r="J41" t="n">
         <x:v>105</x:v>
       </x:c>
+      <x:c r="K41" t="str"/>
+      <x:c r="L41" t="str"/>
+      <x:c r="M41" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N41" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="inlineStr">
@@ -2123,6 +2535,14 @@
       <x:c r="J42" t="n">
         <x:v>105</x:v>
       </x:c>
+      <x:c r="K42" t="str"/>
+      <x:c r="L42" t="str"/>
+      <x:c r="M42" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N42" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="inlineStr">
@@ -2165,6 +2585,14 @@
       <x:c r="J43" t="n">
         <x:v>105</x:v>
       </x:c>
+      <x:c r="K43" t="str"/>
+      <x:c r="L43" t="str"/>
+      <x:c r="M43" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N43" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="inlineStr">
@@ -2207,6 +2635,14 @@
       <x:c r="J44" t="n">
         <x:v>105</x:v>
       </x:c>
+      <x:c r="K44" t="str"/>
+      <x:c r="L44" t="str"/>
+      <x:c r="M44" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N44" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="inlineStr">
@@ -2249,6 +2685,14 @@
       <x:c r="J45" t="n">
         <x:v>105</x:v>
       </x:c>
+      <x:c r="K45" t="str"/>
+      <x:c r="L45" t="str"/>
+      <x:c r="M45" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N45" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="inlineStr">
@@ -2291,6 +2735,14 @@
       <x:c r="J46" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K46" t="str"/>
+      <x:c r="L46" t="str"/>
+      <x:c r="M46" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N46" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="inlineStr">
@@ -2333,6 +2785,14 @@
       <x:c r="J47" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K47" t="str"/>
+      <x:c r="L47" t="str"/>
+      <x:c r="M47" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N47" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="inlineStr">
@@ -2375,6 +2835,14 @@
       <x:c r="J48" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K48" t="str"/>
+      <x:c r="L48" t="str"/>
+      <x:c r="M48" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N48" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="inlineStr">
@@ -2417,6 +2885,14 @@
       <x:c r="J49" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K49" t="str"/>
+      <x:c r="L49" t="str"/>
+      <x:c r="M49" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N49" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="inlineStr">
@@ -2459,6 +2935,14 @@
       <x:c r="J50" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K50" t="str"/>
+      <x:c r="L50" t="str"/>
+      <x:c r="M50" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N50" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="inlineStr">
@@ -2501,6 +2985,14 @@
       <x:c r="J51" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K51" t="str"/>
+      <x:c r="L51" t="str"/>
+      <x:c r="M51" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N51" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" t="inlineStr">
@@ -2543,6 +3035,14 @@
       <x:c r="J52" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K52" t="str"/>
+      <x:c r="L52" t="str"/>
+      <x:c r="M52" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N52" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" t="inlineStr">
@@ -2585,6 +3085,14 @@
       <x:c r="J53" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K53" t="str"/>
+      <x:c r="L53" t="str"/>
+      <x:c r="M53" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N53" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" t="inlineStr">
@@ -2627,6 +3135,14 @@
       <x:c r="J54" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K54" t="str"/>
+      <x:c r="L54" t="str"/>
+      <x:c r="M54" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N54" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" t="inlineStr">
@@ -2669,6 +3185,14 @@
       <x:c r="J55" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K55" t="str"/>
+      <x:c r="L55" t="str"/>
+      <x:c r="M55" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N55" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" t="inlineStr">
@@ -2711,6 +3235,14 @@
       <x:c r="J56" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K56" t="str"/>
+      <x:c r="L56" t="str"/>
+      <x:c r="M56" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N56" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" t="inlineStr">
@@ -2753,6 +3285,14 @@
       <x:c r="J57" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K57" t="str"/>
+      <x:c r="L57" t="str"/>
+      <x:c r="M57" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N57" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" t="inlineStr">
@@ -2795,6 +3335,14 @@
       <x:c r="J58" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K58" t="str"/>
+      <x:c r="L58" t="str"/>
+      <x:c r="M58" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N58" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" t="inlineStr">
@@ -2837,6 +3385,14 @@
       <x:c r="J59" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K59" t="str"/>
+      <x:c r="L59" t="str"/>
+      <x:c r="M59" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N59" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" t="inlineStr">
@@ -2879,6 +3435,14 @@
       <x:c r="J60" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K60" t="str"/>
+      <x:c r="L60" t="str"/>
+      <x:c r="M60" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N60" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" t="inlineStr">
@@ -2921,6 +3485,14 @@
       <x:c r="J61" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K61" t="str"/>
+      <x:c r="L61" t="str"/>
+      <x:c r="M61" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N61" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" t="inlineStr">
@@ -2963,6 +3535,14 @@
       <x:c r="J62" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K62" t="str"/>
+      <x:c r="L62" t="str"/>
+      <x:c r="M62" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N62" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" t="inlineStr">
@@ -3005,6 +3585,14 @@
       <x:c r="J63" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K63" t="str"/>
+      <x:c r="L63" t="str"/>
+      <x:c r="M63" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N63" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" t="inlineStr">
@@ -3047,6 +3635,14 @@
       <x:c r="J64" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K64" t="str"/>
+      <x:c r="L64" t="str"/>
+      <x:c r="M64" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N64" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="inlineStr">
@@ -3089,6 +3685,14 @@
       <x:c r="J65" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K65" t="str"/>
+      <x:c r="L65" t="str"/>
+      <x:c r="M65" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N65" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="inlineStr">
@@ -3131,6 +3735,14 @@
       <x:c r="J66" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K66" t="str"/>
+      <x:c r="L66" t="str"/>
+      <x:c r="M66" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N66" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="inlineStr">
@@ -3173,6 +3785,14 @@
       <x:c r="J67" t="n">
         <x:v>140</x:v>
       </x:c>
+      <x:c r="K67" t="str"/>
+      <x:c r="L67" t="str"/>
+      <x:c r="M67" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N67" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="inlineStr">
@@ -3215,6 +3835,14 @@
       <x:c r="J68" t="n">
         <x:v>135</x:v>
       </x:c>
+      <x:c r="K68" t="str"/>
+      <x:c r="L68" t="str"/>
+      <x:c r="M68" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N68" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="inlineStr">
@@ -3257,6 +3885,14 @@
       <x:c r="J69" t="n">
         <x:v>135</x:v>
       </x:c>
+      <x:c r="K69" t="str"/>
+      <x:c r="L69" t="str"/>
+      <x:c r="M69" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N69" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="inlineStr">
@@ -3299,6 +3935,14 @@
       <x:c r="J70" t="n">
         <x:v>135</x:v>
       </x:c>
+      <x:c r="K70" t="str"/>
+      <x:c r="L70" t="str"/>
+      <x:c r="M70" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N70" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="inlineStr">
@@ -3341,6 +3985,14 @@
       <x:c r="J71" t="n">
         <x:v>135</x:v>
       </x:c>
+      <x:c r="K71" t="str"/>
+      <x:c r="L71" t="str"/>
+      <x:c r="M71" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N71" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="inlineStr">
@@ -3383,6 +4035,14 @@
       <x:c r="J72" t="n">
         <x:v>135</x:v>
       </x:c>
+      <x:c r="K72" t="str"/>
+      <x:c r="L72" t="str"/>
+      <x:c r="M72" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N72" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="inlineStr">
@@ -3425,6 +4085,14 @@
       <x:c r="J73" t="n">
         <x:v>135</x:v>
       </x:c>
+      <x:c r="K73" t="str"/>
+      <x:c r="L73" t="str"/>
+      <x:c r="M73" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N73" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="inlineStr">
@@ -3467,6 +4135,14 @@
       <x:c r="J74" t="n">
         <x:v>135</x:v>
       </x:c>
+      <x:c r="K74" t="str"/>
+      <x:c r="L74" t="str"/>
+      <x:c r="M74" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N74" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="inlineStr">
@@ -3509,6 +4185,14 @@
       <x:c r="J75" t="n">
         <x:v>135</x:v>
       </x:c>
+      <x:c r="K75" t="str"/>
+      <x:c r="L75" t="str"/>
+      <x:c r="M75" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N75" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="inlineStr">
@@ -3551,6 +4235,18 @@
       <x:c r="J76" t="n">
         <x:v>125</x:v>
       </x:c>
+      <x:c r="K76" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/立式灯柱-1.png</x:v>
+      </x:c>
+      <x:c r="L76" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/立式灯柱-1.png</x:v>
+      </x:c>
+      <x:c r="M76" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N76" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="inlineStr">
@@ -3593,6 +4289,18 @@
       <x:c r="J77" t="n">
         <x:v>125</x:v>
       </x:c>
+      <x:c r="K77" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/立式灯柱-2.png</x:v>
+      </x:c>
+      <x:c r="L77" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/立式灯柱-2.png</x:v>
+      </x:c>
+      <x:c r="M77" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N77" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="inlineStr">
@@ -3635,6 +4343,18 @@
       <x:c r="J78" t="n">
         <x:v>125</x:v>
       </x:c>
+      <x:c r="K78" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/立式灯柱-3.png</x:v>
+      </x:c>
+      <x:c r="L78" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/立式灯柱-3.png</x:v>
+      </x:c>
+      <x:c r="M78" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N78" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="inlineStr">
@@ -3677,6 +4397,18 @@
       <x:c r="J79" t="n">
         <x:v>125</x:v>
       </x:c>
+      <x:c r="K79" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/立式灯柱-4.png</x:v>
+      </x:c>
+      <x:c r="L79" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/立式灯柱-4.png</x:v>
+      </x:c>
+      <x:c r="M79" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N79" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="inlineStr">
@@ -3719,6 +4451,18 @@
       <x:c r="J80" t="n">
         <x:v>125</x:v>
       </x:c>
+      <x:c r="K80" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/立式灯柱-5.png</x:v>
+      </x:c>
+      <x:c r="L80" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/立式灯柱-5.png</x:v>
+      </x:c>
+      <x:c r="M80" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N80" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" t="inlineStr">
@@ -3761,6 +4505,18 @@
       <x:c r="J81" t="n">
         <x:v>125</x:v>
       </x:c>
+      <x:c r="K81" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/立式灯柱-6.png</x:v>
+      </x:c>
+      <x:c r="L81" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/立式灯柱-6.png</x:v>
+      </x:c>
+      <x:c r="M81" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N81" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" t="inlineStr">
@@ -3803,6 +4559,18 @@
       <x:c r="J82" t="n">
         <x:v>125</x:v>
       </x:c>
+      <x:c r="K82" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/立式灯柱-7.png</x:v>
+      </x:c>
+      <x:c r="L82" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/立式灯柱-7.png</x:v>
+      </x:c>
+      <x:c r="M82" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N82" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" t="inlineStr">
@@ -3845,6 +4613,18 @@
       <x:c r="J83" t="n">
         <x:v>125</x:v>
       </x:c>
+      <x:c r="K83" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/立式灯柱-8.png</x:v>
+      </x:c>
+      <x:c r="L83" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/立式灯柱-8.png</x:v>
+      </x:c>
+      <x:c r="M83" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="N83" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" t="inlineStr">
@@ -3887,6 +4667,14 @@
       <x:c r="J84" t="n">
         <x:v>205</x:v>
       </x:c>
+      <x:c r="K84" t="str"/>
+      <x:c r="L84" t="str"/>
+      <x:c r="M84" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N84" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" t="inlineStr">
@@ -3929,6 +4717,14 @@
       <x:c r="J85" t="n">
         <x:v>205</x:v>
       </x:c>
+      <x:c r="K85" t="str"/>
+      <x:c r="L85" t="str"/>
+      <x:c r="M85" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N85" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" t="inlineStr">
@@ -3971,6 +4767,14 @@
       <x:c r="J86" t="n">
         <x:v>205</x:v>
       </x:c>
+      <x:c r="K86" t="str"/>
+      <x:c r="L86" t="str"/>
+      <x:c r="M86" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N86" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" t="inlineStr">
@@ -4013,6 +4817,14 @@
       <x:c r="J87" t="n">
         <x:v>205</x:v>
       </x:c>
+      <x:c r="K87" t="str"/>
+      <x:c r="L87" t="str"/>
+      <x:c r="M87" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N87" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" t="inlineStr">
@@ -4055,6 +4867,14 @@
       <x:c r="J88" t="n">
         <x:v>205</x:v>
       </x:c>
+      <x:c r="K88" t="str"/>
+      <x:c r="L88" t="str"/>
+      <x:c r="M88" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N88" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" t="inlineStr">
@@ -4097,6 +4917,14 @@
       <x:c r="J89" t="n">
         <x:v>205</x:v>
       </x:c>
+      <x:c r="K89" t="str"/>
+      <x:c r="L89" t="str"/>
+      <x:c r="M89" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N89" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" t="inlineStr">
@@ -4139,6 +4967,14 @@
       <x:c r="J90" t="n">
         <x:v>205</x:v>
       </x:c>
+      <x:c r="K90" t="str"/>
+      <x:c r="L90" t="str"/>
+      <x:c r="M90" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="N90" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" t="inlineStr">
@@ -4181,6 +5017,14 @@
       <x:c r="J91" t="n">
         <x:v>85</x:v>
       </x:c>
+      <x:c r="K91" t="str"/>
+      <x:c r="L91" t="str"/>
+      <x:c r="M91" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N91" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" t="inlineStr">
@@ -4223,6 +5067,14 @@
       <x:c r="J92" t="n">
         <x:v>85</x:v>
       </x:c>
+      <x:c r="K92" t="str"/>
+      <x:c r="L92" t="str"/>
+      <x:c r="M92" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N92" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" t="inlineStr">
@@ -4265,6 +5117,14 @@
       <x:c r="J93" t="n">
         <x:v>85</x:v>
       </x:c>
+      <x:c r="K93" t="str"/>
+      <x:c r="L93" t="str"/>
+      <x:c r="M93" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N93" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" t="inlineStr">
@@ -4307,6 +5167,14 @@
       <x:c r="J94" t="n">
         <x:v>85</x:v>
       </x:c>
+      <x:c r="K94" t="str"/>
+      <x:c r="L94" t="str"/>
+      <x:c r="M94" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N94" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" t="inlineStr">
@@ -4349,6 +5217,14 @@
       <x:c r="J95" t="n">
         <x:v>85</x:v>
       </x:c>
+      <x:c r="K95" t="str"/>
+      <x:c r="L95" t="str"/>
+      <x:c r="M95" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N95" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" t="inlineStr">
@@ -4391,6 +5267,14 @@
       <x:c r="J96" t="n">
         <x:v>85</x:v>
       </x:c>
+      <x:c r="K96" t="str"/>
+      <x:c r="L96" t="str"/>
+      <x:c r="M96" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N96" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" t="inlineStr">
@@ -4433,6 +5317,14 @@
       <x:c r="J97" t="n">
         <x:v>85</x:v>
       </x:c>
+      <x:c r="K97" t="str"/>
+      <x:c r="L97" t="str"/>
+      <x:c r="M97" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N97" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" t="inlineStr">
@@ -4475,6 +5367,14 @@
       <x:c r="J98" t="n">
         <x:v>85</x:v>
       </x:c>
+      <x:c r="K98" t="str"/>
+      <x:c r="L98" t="str"/>
+      <x:c r="M98" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N98" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" t="inlineStr">
@@ -4517,6 +5417,14 @@
       <x:c r="J99" t="n">
         <x:v>85</x:v>
       </x:c>
+      <x:c r="K99" t="str"/>
+      <x:c r="L99" t="str"/>
+      <x:c r="M99" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N99" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" t="inlineStr">
@@ -4559,6 +5467,14 @@
       <x:c r="J100" t="n">
         <x:v>150</x:v>
       </x:c>
+      <x:c r="K100" t="str"/>
+      <x:c r="L100" t="str"/>
+      <x:c r="M100" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N100" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" t="inlineStr">
@@ -4601,6 +5517,14 @@
       <x:c r="J101" t="n">
         <x:v>150</x:v>
       </x:c>
+      <x:c r="K101" t="str"/>
+      <x:c r="L101" t="str"/>
+      <x:c r="M101" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N101" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" t="inlineStr">
@@ -4643,6 +5567,14 @@
       <x:c r="J102" t="n">
         <x:v>150</x:v>
       </x:c>
+      <x:c r="K102" t="str"/>
+      <x:c r="L102" t="str"/>
+      <x:c r="M102" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N102" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" t="inlineStr">
@@ -4685,6 +5617,14 @@
       <x:c r="J103" t="n">
         <x:v>150</x:v>
       </x:c>
+      <x:c r="K103" t="str"/>
+      <x:c r="L103" t="str"/>
+      <x:c r="M103" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N103" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" t="inlineStr">
@@ -4727,6 +5667,14 @@
       <x:c r="J104" t="n">
         <x:v>150</x:v>
       </x:c>
+      <x:c r="K104" t="str"/>
+      <x:c r="L104" t="str"/>
+      <x:c r="M104" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N104" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" t="inlineStr">
@@ -4769,6 +5717,14 @@
       <x:c r="J105" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K105" t="str"/>
+      <x:c r="L105" t="str"/>
+      <x:c r="M105" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N105" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" t="inlineStr">
@@ -4811,6 +5767,14 @@
       <x:c r="J106" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K106" t="str"/>
+      <x:c r="L106" t="str"/>
+      <x:c r="M106" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N106" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" t="inlineStr">
@@ -4853,6 +5817,14 @@
       <x:c r="J107" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K107" t="str"/>
+      <x:c r="L107" t="str"/>
+      <x:c r="M107" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N107" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" t="inlineStr">
@@ -4895,6 +5867,14 @@
       <x:c r="J108" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K108" t="str"/>
+      <x:c r="L108" t="str"/>
+      <x:c r="M108" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N108" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" t="inlineStr">
@@ -4937,6 +5917,14 @@
       <x:c r="J109" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K109" t="str"/>
+      <x:c r="L109" t="str"/>
+      <x:c r="M109" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N109" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" t="inlineStr">
@@ -4979,6 +5967,14 @@
       <x:c r="J110" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K110" t="str"/>
+      <x:c r="L110" t="str"/>
+      <x:c r="M110" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N110" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" t="inlineStr">
@@ -5021,6 +6017,14 @@
       <x:c r="J111" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K111" t="str"/>
+      <x:c r="L111" t="str"/>
+      <x:c r="M111" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N111" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" t="inlineStr">
@@ -5063,6 +6067,14 @@
       <x:c r="J112" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K112" t="str"/>
+      <x:c r="L112" t="str"/>
+      <x:c r="M112" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N112" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" t="inlineStr">
@@ -5105,6 +6117,14 @@
       <x:c r="J113" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K113" t="str"/>
+      <x:c r="L113" t="str"/>
+      <x:c r="M113" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N113" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" t="inlineStr">
@@ -5147,6 +6167,14 @@
       <x:c r="J114" t="n">
         <x:v>90</x:v>
       </x:c>
+      <x:c r="K114" t="str"/>
+      <x:c r="L114" t="str"/>
+      <x:c r="M114" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N114" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" t="inlineStr">
@@ -5189,6 +6217,14 @@
       <x:c r="J115" t="n">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="K115" t="str"/>
+      <x:c r="L115" t="str"/>
+      <x:c r="M115" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N115" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" t="inlineStr">
@@ -5231,6 +6267,14 @@
       <x:c r="J116" t="n">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="K116" t="str"/>
+      <x:c r="L116" t="str"/>
+      <x:c r="M116" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N116" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" t="inlineStr">
@@ -5273,6 +6317,14 @@
       <x:c r="J117" t="n">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="K117" t="str"/>
+      <x:c r="L117" t="str"/>
+      <x:c r="M117" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N117" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" t="inlineStr">
@@ -5315,6 +6367,14 @@
       <x:c r="J118" t="n">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="K118" t="str"/>
+      <x:c r="L118" t="str"/>
+      <x:c r="M118" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N118" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" t="inlineStr">
@@ -5357,6 +6417,14 @@
       <x:c r="J119" t="n">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="K119" t="str"/>
+      <x:c r="L119" t="str"/>
+      <x:c r="M119" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N119" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" t="inlineStr">
@@ -5399,6 +6467,14 @@
       <x:c r="J120" t="n">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="K120" t="str"/>
+      <x:c r="L120" t="str"/>
+      <x:c r="M120" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N120" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" t="inlineStr">
@@ -5441,6 +6517,14 @@
       <x:c r="J121" t="n">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="K121" t="str"/>
+      <x:c r="L121" t="str"/>
+      <x:c r="M121" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N121" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" t="inlineStr">
@@ -5483,6 +6567,14 @@
       <x:c r="J122" t="n">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="K122" t="str"/>
+      <x:c r="L122" t="str"/>
+      <x:c r="M122" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N122" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" t="inlineStr">
@@ -5525,6 +6617,14 @@
       <x:c r="J123" t="n">
         <x:v>95</x:v>
       </x:c>
+      <x:c r="K123" t="str"/>
+      <x:c r="L123" t="str"/>
+      <x:c r="M123" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N123" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" t="inlineStr">
@@ -5567,6 +6667,14 @@
       <x:c r="J124" t="n">
         <x:v>145</x:v>
       </x:c>
+      <x:c r="K124" t="str"/>
+      <x:c r="L124" t="str"/>
+      <x:c r="M124" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N124" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" t="inlineStr">
@@ -5609,6 +6717,14 @@
       <x:c r="J125" t="n">
         <x:v>145</x:v>
       </x:c>
+      <x:c r="K125" t="str"/>
+      <x:c r="L125" t="str"/>
+      <x:c r="M125" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N125" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126" t="inlineStr">
@@ -5651,6 +6767,14 @@
       <x:c r="J126" t="n">
         <x:v>145</x:v>
       </x:c>
+      <x:c r="K126" t="str"/>
+      <x:c r="L126" t="str"/>
+      <x:c r="M126" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N126" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" t="inlineStr">
@@ -5693,6 +6817,14 @@
       <x:c r="J127" t="n">
         <x:v>145</x:v>
       </x:c>
+      <x:c r="K127" t="str"/>
+      <x:c r="L127" t="str"/>
+      <x:c r="M127" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N127" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" t="inlineStr">
@@ -5735,6 +6867,14 @@
       <x:c r="J128" t="n">
         <x:v>145</x:v>
       </x:c>
+      <x:c r="K128" t="str"/>
+      <x:c r="L128" t="str"/>
+      <x:c r="M128" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N128" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" t="inlineStr">
@@ -5777,6 +6917,14 @@
       <x:c r="J129" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K129" t="str"/>
+      <x:c r="L129" t="str"/>
+      <x:c r="M129" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N129" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" t="inlineStr">
@@ -5819,6 +6967,14 @@
       <x:c r="J130" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K130" t="str"/>
+      <x:c r="L130" t="str"/>
+      <x:c r="M130" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N130" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" t="inlineStr">
@@ -5861,6 +7017,14 @@
       <x:c r="J131" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K131" t="str"/>
+      <x:c r="L131" t="str"/>
+      <x:c r="M131" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N131" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" t="inlineStr">
@@ -5903,6 +7067,14 @@
       <x:c r="J132" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K132" t="str"/>
+      <x:c r="L132" t="str"/>
+      <x:c r="M132" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N132" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" t="inlineStr">
@@ -5945,6 +7117,14 @@
       <x:c r="J133" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K133" t="str"/>
+      <x:c r="L133" t="str"/>
+      <x:c r="M133" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N133" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="134">
       <x:c r="A134" t="inlineStr">
@@ -5987,6 +7167,14 @@
       <x:c r="J134" t="n">
         <x:v>155</x:v>
       </x:c>
+      <x:c r="K134" t="str"/>
+      <x:c r="L134" t="str"/>
+      <x:c r="M134" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N134" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="135">
       <x:c r="A135" t="inlineStr">
@@ -6029,6 +7217,14 @@
       <x:c r="J135" t="n">
         <x:v>185</x:v>
       </x:c>
+      <x:c r="K135" t="str"/>
+      <x:c r="L135" t="str"/>
+      <x:c r="M135" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N135" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="136">
       <x:c r="A136" t="inlineStr">
@@ -6071,6 +7267,14 @@
       <x:c r="J136" t="n">
         <x:v>75</x:v>
       </x:c>
+      <x:c r="K136" t="str"/>
+      <x:c r="L136" t="str"/>
+      <x:c r="M136" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="N136" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" t="inlineStr">
@@ -6113,6 +7317,14 @@
       <x:c r="J137" t="n">
         <x:v>125</x:v>
       </x:c>
+      <x:c r="K137" t="str"/>
+      <x:c r="L137" t="str"/>
+      <x:c r="M137" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N137" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="138">
       <x:c r="A138" t="inlineStr">
@@ -6155,6 +7367,14 @@
       <x:c r="J138" t="n">
         <x:v>170</x:v>
       </x:c>
+      <x:c r="K138" t="str"/>
+      <x:c r="L138" t="str"/>
+      <x:c r="M138" s="2" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N138" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
     <x:row r="139">
       <x:c r="A139" t="inlineStr">
@@ -6197,6 +7417,14 @@
       <x:c r="J139" t="n">
         <x:v>60</x:v>
       </x:c>
+      <x:c r="K139" t="str"/>
+      <x:c r="L139" t="str"/>
+      <x:c r="M139" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N139" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" t="inlineStr">
@@ -6239,6 +7467,14 @@
       <x:c r="J140" t="n">
         <x:v>75</x:v>
       </x:c>
+      <x:c r="K140" t="str"/>
+      <x:c r="L140" t="str"/>
+      <x:c r="M140" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N140" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="141">
       <x:c r="A141" t="inlineStr">
@@ -6281,6 +7517,14 @@
       <x:c r="J141" t="n">
         <x:v>120</x:v>
       </x:c>
+      <x:c r="K141" t="str"/>
+      <x:c r="L141" t="str"/>
+      <x:c r="M141" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N141" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="142">
       <x:c r="A142" t="inlineStr">
@@ -6323,6 +7567,14 @@
       <x:c r="J142" t="n">
         <x:v>115</x:v>
       </x:c>
+      <x:c r="K142" t="str"/>
+      <x:c r="L142" t="str"/>
+      <x:c r="M142" s="2" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="N142" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" t="inlineStr">
@@ -6365,6 +7617,14 @@
       <x:c r="J143" t="n">
         <x:v>215</x:v>
       </x:c>
+      <x:c r="K143" t="str"/>
+      <x:c r="L143" t="str"/>
+      <x:c r="M143" s="2" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="N143" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" t="inlineStr">
@@ -6407,6 +7667,14 @@
       <x:c r="J144" t="n">
         <x:v>135</x:v>
       </x:c>
+      <x:c r="K144" t="str"/>
+      <x:c r="L144" t="str"/>
+      <x:c r="M144" s="2" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N144" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="145">
       <x:c r="A145" t="inlineStr">
@@ -6449,6 +7717,14 @@
       <x:c r="J145" t="n">
         <x:v>100</x:v>
       </x:c>
+      <x:c r="K145" t="str"/>
+      <x:c r="L145" t="str"/>
+      <x:c r="M145" s="2" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="N145" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="146">
       <x:c r="A146" t="inlineStr">
@@ -6490,6 +7766,454 @@
       </x:c>
       <x:c r="J146" t="n">
         <x:v>100</x:v>
+      </x:c>
+      <x:c r="K146" t="str"/>
+      <x:c r="L146" t="str"/>
+      <x:c r="M146" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N146" s="2" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>cabinet_01</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>cabinet_01</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>立柜·01</x:v>
+      </x:c>
+      <x:c r="D147" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="E147" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="F147" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G147" t="str">
+        <x:v>Assets/PC ui/Scene/furniture/cabinet_01.png</x:v>
+      </x:c>
+      <x:c r="H147" t="str">
+        <x:v>#DBC4A0</x:v>
+      </x:c>
+      <x:c r="I147" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J147" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K147" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/Frame 114.png</x:v>
+      </x:c>
+      <x:c r="L147" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/Frame 104.png</x:v>
+      </x:c>
+      <x:c r="M147" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N147" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>cabinet_02</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>cabinet_02</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>立柜·02</x:v>
+      </x:c>
+      <x:c r="D148" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="E148" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F148" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G148" t="str">
+        <x:v>Assets/PC ui/Scene/furniture/cabinet_02.png</x:v>
+      </x:c>
+      <x:c r="H148" t="str">
+        <x:v>#E8B2A6</x:v>
+      </x:c>
+      <x:c r="I148" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J148" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K148" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/Frame 115.png</x:v>
+      </x:c>
+      <x:c r="L148" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/Frame 105.png</x:v>
+      </x:c>
+      <x:c r="M148" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N148" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>cabinet_03</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>cabinet_03</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>立柜·03</x:v>
+      </x:c>
+      <x:c r="D149" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="E149" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="F149" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G149" t="str">
+        <x:v>Assets/PC ui/Scene/furniture/cabinet_03.png</x:v>
+      </x:c>
+      <x:c r="H149" t="str">
+        <x:v>#959E78</x:v>
+      </x:c>
+      <x:c r="I149" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="J149" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K149" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/Frame 113.png</x:v>
+      </x:c>
+      <x:c r="L149" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/Frame 103.png</x:v>
+      </x:c>
+      <x:c r="M149" s="2" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N149" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>cabinet_04</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>cabinet_04</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>立柜·04</x:v>
+      </x:c>
+      <x:c r="D150" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="E150" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F150" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G150" t="str">
+        <x:v>Assets/PC ui/Scene/furniture/cabinet_04.png</x:v>
+      </x:c>
+      <x:c r="H150" t="str">
+        <x:v>#ADC2C8</x:v>
+      </x:c>
+      <x:c r="I150" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J150" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K150" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/Frame 112.png</x:v>
+      </x:c>
+      <x:c r="L150" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/Frame 102.png</x:v>
+      </x:c>
+      <x:c r="M150" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N150" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>cabinet_05</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>cabinet_05</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>立柜·05</x:v>
+      </x:c>
+      <x:c r="D151" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="E151" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="F151" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G151" t="str">
+        <x:v>Assets/PC ui/Scene/furniture/cabinet_05.png</x:v>
+      </x:c>
+      <x:c r="H151" t="str">
+        <x:v>#BFAEC4</x:v>
+      </x:c>
+      <x:c r="I151" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J151" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K151" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/Frame 111.png</x:v>
+      </x:c>
+      <x:c r="L151" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/Frame 101.png</x:v>
+      </x:c>
+      <x:c r="M151" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N151" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>cabinet_06</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>cabinet_06</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>立柜·06</x:v>
+      </x:c>
+      <x:c r="D152" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="E152" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="F152" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G152" t="str">
+        <x:v>Assets/PC ui/Scene/furniture/cabinet_06.png</x:v>
+      </x:c>
+      <x:c r="H152" t="str">
+        <x:v>#D9A566</x:v>
+      </x:c>
+      <x:c r="I152" t="n">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="J152" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K152" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/Frame 110.png</x:v>
+      </x:c>
+      <x:c r="L152" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/Frame 100.png</x:v>
+      </x:c>
+      <x:c r="M152" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N152" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>cabinet_07</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>cabinet_07</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>立柜·07</x:v>
+      </x:c>
+      <x:c r="D153" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="E153" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="F153" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G153" t="str">
+        <x:v>Assets/PC ui/Scene/furniture/cabinet_07.png</x:v>
+      </x:c>
+      <x:c r="H153" t="str">
+        <x:v>#ABBBBF</x:v>
+      </x:c>
+      <x:c r="I153" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J153" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K153" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/Frame 109.png</x:v>
+      </x:c>
+      <x:c r="L153" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/Frame 99.png</x:v>
+      </x:c>
+      <x:c r="M153" s="2" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="N153" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>cabinet_08</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>cabinet_08</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>立柜·08</x:v>
+      </x:c>
+      <x:c r="D154" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="E154" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F154" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G154" t="str">
+        <x:v>Assets/PC ui/Scene/furniture/cabinet_08.png</x:v>
+      </x:c>
+      <x:c r="H154" t="str">
+        <x:v>#BEB0A0</x:v>
+      </x:c>
+      <x:c r="I154" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J154" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K154" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/Frame 116.png</x:v>
+      </x:c>
+      <x:c r="L154" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/Frame 106.png</x:v>
+      </x:c>
+      <x:c r="M154" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N154" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>cabinet_09</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>cabinet_09</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>立柜·09</x:v>
+      </x:c>
+      <x:c r="D155" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="E155" t="n">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F155" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G155" t="str">
+        <x:v>Assets/PC ui/Scene/furniture/cabinet_09.png</x:v>
+      </x:c>
+      <x:c r="H155" t="str">
+        <x:v>#E59179</x:v>
+      </x:c>
+      <x:c r="I155" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="J155" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K155" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/Frame 117.png</x:v>
+      </x:c>
+      <x:c r="L155" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/Frame 107.png</x:v>
+      </x:c>
+      <x:c r="M155" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="N155" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>cabinet_10</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>cabinet_10</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>立柜·10</x:v>
+      </x:c>
+      <x:c r="D156" t="str">
+        <x:v>cabinet</x:v>
+      </x:c>
+      <x:c r="E156" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="F156" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="G156" t="str">
+        <x:v>Assets/PC ui/Scene/furniture/cabinet_10.png</x:v>
+      </x:c>
+      <x:c r="H156" t="str">
+        <x:v>#AAC1BF</x:v>
+      </x:c>
+      <x:c r="I156" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J156" t="n">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="K156" t="str">
+        <x:v>Assets/PC ui 2.0/store/左侧家具图标/Frame 108.png</x:v>
+      </x:c>
+      <x:c r="L156" t="str">
+        <x:v>Assets/PC ui 2.0/store/右侧家具图标/Frame 98.png</x:v>
+      </x:c>
+      <x:c r="M156" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="N156" s="2" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Excel/家具表.xlsx
+++ b/Excel/家具表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具" sheetId="1" r:id="R3c458a2154e54295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="家具" sheetId="1" r:id="R8736c2ebf33a43e2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -520,10 +520,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-1.png</x:v>
       </x:c>
       <x:c r="M3" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N3" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -574,10 +574,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-2.png</x:v>
       </x:c>
       <x:c r="M4" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N4" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -628,10 +628,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-3.png</x:v>
       </x:c>
       <x:c r="M5" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N5" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -682,10 +682,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-4.png</x:v>
       </x:c>
       <x:c r="M6" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N6" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -736,10 +736,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-5.png</x:v>
       </x:c>
       <x:c r="M7" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N7" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -790,10 +790,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/台灯-6.png</x:v>
       </x:c>
       <x:c r="M8" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N8" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -840,10 +840,10 @@
       <x:c r="K9" t="str"/>
       <x:c r="L9" t="str"/>
       <x:c r="M9" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="N9" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -890,10 +890,10 @@
       <x:c r="K10" t="str"/>
       <x:c r="L10" t="str"/>
       <x:c r="M10" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="N10" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -940,10 +940,10 @@
       <x:c r="K11" t="str"/>
       <x:c r="L11" t="str"/>
       <x:c r="M11" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="N11" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -990,10 +990,10 @@
       <x:c r="K12" t="str"/>
       <x:c r="L12" t="str"/>
       <x:c r="M12" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="N12" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1040,10 +1040,10 @@
       <x:c r="K13" t="str"/>
       <x:c r="L13" t="str"/>
       <x:c r="M13" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="N13" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1090,10 +1090,10 @@
       <x:c r="K14" t="str"/>
       <x:c r="L14" t="str"/>
       <x:c r="M14" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="N14" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1140,10 +1140,10 @@
       <x:c r="K15" t="str"/>
       <x:c r="L15" t="str"/>
       <x:c r="M15" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="N15" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1190,10 +1190,10 @@
       <x:c r="K16" t="str"/>
       <x:c r="L16" t="str"/>
       <x:c r="M16" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="N16" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1240,7 +1240,7 @@
       <x:c r="K17" t="str"/>
       <x:c r="L17" t="str"/>
       <x:c r="M17" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N17" s="2" t="n">
         <x:v>1</x:v>
@@ -1290,7 +1290,7 @@
       <x:c r="K18" t="str"/>
       <x:c r="L18" t="str"/>
       <x:c r="M18" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N18" s="2" t="n">
         <x:v>1</x:v>
@@ -1340,7 +1340,7 @@
       <x:c r="K19" t="str"/>
       <x:c r="L19" t="str"/>
       <x:c r="M19" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N19" s="2" t="n">
         <x:v>1</x:v>
@@ -1390,7 +1390,7 @@
       <x:c r="K20" t="str"/>
       <x:c r="L20" t="str"/>
       <x:c r="M20" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N20" s="2" t="n">
         <x:v>1</x:v>
@@ -1440,10 +1440,10 @@
       <x:c r="K21" t="str"/>
       <x:c r="L21" t="str"/>
       <x:c r="M21" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N21" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1490,10 +1490,10 @@
       <x:c r="K22" t="str"/>
       <x:c r="L22" t="str"/>
       <x:c r="M22" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N22" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1540,10 +1540,10 @@
       <x:c r="K23" t="str"/>
       <x:c r="L23" t="str"/>
       <x:c r="M23" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N23" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1590,10 +1590,10 @@
       <x:c r="K24" t="str"/>
       <x:c r="L24" t="str"/>
       <x:c r="M24" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N24" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1640,10 +1640,10 @@
       <x:c r="K25" t="str"/>
       <x:c r="L25" t="str"/>
       <x:c r="M25" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N25" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1690,10 +1690,10 @@
       <x:c r="K26" t="str"/>
       <x:c r="L26" t="str"/>
       <x:c r="M26" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N26" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -1740,10 +1740,10 @@
       <x:c r="K27" t="str"/>
       <x:c r="L27" t="str"/>
       <x:c r="M27" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N27" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -1790,10 +1790,10 @@
       <x:c r="K28" t="str"/>
       <x:c r="L28" t="str"/>
       <x:c r="M28" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N28" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -1844,10 +1844,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_10 2.png</x:v>
       </x:c>
       <x:c r="M29" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N29" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1898,10 +1898,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_04 2.png</x:v>
       </x:c>
       <x:c r="M30" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N30" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -1952,10 +1952,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_09 2.png</x:v>
       </x:c>
       <x:c r="M31" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N31" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2006,10 +2006,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_05 2.png</x:v>
       </x:c>
       <x:c r="M32" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N32" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -2060,10 +2060,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_06 2.png</x:v>
       </x:c>
       <x:c r="M33" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N33" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2114,10 +2114,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_07 2.png</x:v>
       </x:c>
       <x:c r="M34" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N34" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2168,10 +2168,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_08 2.png</x:v>
       </x:c>
       <x:c r="M35" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N35" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -2222,10 +2222,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_01 2.png</x:v>
       </x:c>
       <x:c r="M36" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N36" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -2276,10 +2276,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_02 2.png</x:v>
       </x:c>
       <x:c r="M37" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N37" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -2330,10 +2330,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_11 2.png</x:v>
       </x:c>
       <x:c r="M38" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N38" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -2384,10 +2384,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_12 2.png</x:v>
       </x:c>
       <x:c r="M39" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N39" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2438,10 +2438,10 @@
         <x:v>Assets/PC ui 2.0/store/右侧家具图标/armchair_03 2.png</x:v>
       </x:c>
       <x:c r="M40" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="N40" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2488,7 +2488,7 @@
       <x:c r="K41" t="str"/>
       <x:c r="L41" t="str"/>
       <x:c r="M41" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N41" s="2" t="n">
         <x:v>1</x:v>
@@ -2538,7 +2538,7 @@
       <x:c r="K42" t="str"/>
       <x:c r="L42" t="str"/>
       <x:c r="M42" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N42" s="2" t="n">
         <x:v>1</x:v>
@@ -2588,7 +2588,7 @@
       <x:c r="K43" t="str"/>
       <x:c r="L43" t="str"/>
       <x:c r="M43" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N43" s="2" t="n">
         <x:v>1</x:v>
@@ -2638,7 +2638,7 @@
       <x:c r="K44" t="str"/>
       <x:c r="L44" t="str"/>
       <x:c r="M44" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N44" s="2" t="n">
         <x:v>1</x:v>
@@ -2688,7 +2688,7 @@
       <x:c r="K45" t="str"/>
       <x:c r="L45" t="str"/>
       <x:c r="M45" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N45" s="2" t="n">
         <x:v>1</x:v>
@@ -4670,10 +4670,10 @@
       <x:c r="K84" t="str"/>
       <x:c r="L84" t="str"/>
       <x:c r="M84" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N84" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -4720,10 +4720,10 @@
       <x:c r="K85" t="str"/>
       <x:c r="L85" t="str"/>
       <x:c r="M85" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N85" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -4770,10 +4770,10 @@
       <x:c r="K86" t="str"/>
       <x:c r="L86" t="str"/>
       <x:c r="M86" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N86" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -4820,10 +4820,10 @@
       <x:c r="K87" t="str"/>
       <x:c r="L87" t="str"/>
       <x:c r="M87" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N87" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -4870,10 +4870,10 @@
       <x:c r="K88" t="str"/>
       <x:c r="L88" t="str"/>
       <x:c r="M88" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N88" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -4920,10 +4920,10 @@
       <x:c r="K89" t="str"/>
       <x:c r="L89" t="str"/>
       <x:c r="M89" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N89" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -4970,10 +4970,10 @@
       <x:c r="K90" t="str"/>
       <x:c r="L90" t="str"/>
       <x:c r="M90" s="2" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N90" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -5470,10 +5470,10 @@
       <x:c r="K100" t="str"/>
       <x:c r="L100" t="str"/>
       <x:c r="M100" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N100" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -5520,10 +5520,10 @@
       <x:c r="K101" t="str"/>
       <x:c r="L101" t="str"/>
       <x:c r="M101" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N101" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -5570,10 +5570,10 @@
       <x:c r="K102" t="str"/>
       <x:c r="L102" t="str"/>
       <x:c r="M102" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N102" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -5620,10 +5620,10 @@
       <x:c r="K103" t="str"/>
       <x:c r="L103" t="str"/>
       <x:c r="M103" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N103" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -5670,10 +5670,10 @@
       <x:c r="K104" t="str"/>
       <x:c r="L104" t="str"/>
       <x:c r="M104" s="2" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N104" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="105">
@@ -5723,7 +5723,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="N105" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -5773,7 +5773,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="N106" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="107">
@@ -5823,7 +5823,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="N107" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="108">
@@ -5873,7 +5873,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="N108" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="109">
@@ -5923,7 +5923,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="N109" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="110">
@@ -5973,7 +5973,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="N110" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -6023,7 +6023,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="N111" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -6073,7 +6073,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="N112" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -6123,7 +6123,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="N113" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -6173,7 +6173,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="N114" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -6673,7 +6673,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="N124" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="125">
@@ -6723,7 +6723,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="N125" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="126">
@@ -6773,7 +6773,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="N126" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -6823,7 +6823,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="N127" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="128">
@@ -6873,7 +6873,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="N128" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="129">
@@ -6923,7 +6923,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N129" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -6973,7 +6973,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N130" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="131">
@@ -7023,7 +7023,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N131" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="132">
@@ -7073,7 +7073,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N132" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -7123,7 +7123,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N133" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="134">
@@ -7173,7 +7173,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N134" s="2" t="n">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="135">
@@ -7223,7 +7223,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N135" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="136">
@@ -7320,10 +7320,10 @@
       <x:c r="K137" t="str"/>
       <x:c r="L137" t="str"/>
       <x:c r="M137" s="2" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="N137" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="138">
@@ -7370,10 +7370,10 @@
       <x:c r="K138" t="str"/>
       <x:c r="L138" t="str"/>
       <x:c r="M138" s="2" t="n">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="N138" s="2" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="139">
@@ -7470,7 +7470,7 @@
       <x:c r="K140" t="str"/>
       <x:c r="L140" t="str"/>
       <x:c r="M140" s="2" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="N140" s="2" t="n">
         <x:v>1</x:v>
@@ -7520,7 +7520,7 @@
       <x:c r="K141" t="str"/>
       <x:c r="L141" t="str"/>
       <x:c r="M141" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="N141" s="2" t="n">
         <x:v>1</x:v>
@@ -7573,7 +7573,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="N142" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="143">
@@ -7620,10 +7620,10 @@
       <x:c r="K143" t="str"/>
       <x:c r="L143" t="str"/>
       <x:c r="M143" s="2" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="N143" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="144">
@@ -7673,7 +7673,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="N144" s="2" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="145">
@@ -7720,10 +7720,10 @@
       <x:c r="K145" t="str"/>
       <x:c r="L145" t="str"/>
       <x:c r="M145" s="2" t="n">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="N145" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="146">
@@ -7817,7 +7817,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N147" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="148">
@@ -7861,7 +7861,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N148" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="149">
@@ -7905,7 +7905,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="N149" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="150">
@@ -7949,7 +7949,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N150" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="151">
@@ -7993,7 +7993,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="N151" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="152">
@@ -8037,7 +8037,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="N152" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -8081,7 +8081,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="N153" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -8125,7 +8125,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N154" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="155">
@@ -8169,7 +8169,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="N155" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -8213,7 +8213,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N156" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
